--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497190</v>
+        <v>121497209</v>
       </c>
       <c r="B2" t="n">
-        <v>79686</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549134</v>
+        <v>549014</v>
       </c>
       <c r="R2" t="n">
-        <v>7198295</v>
+        <v>7198006</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497178</v>
+        <v>121497186</v>
       </c>
       <c r="B3" t="n">
-        <v>79714</v>
+        <v>79686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549168</v>
+        <v>549143</v>
       </c>
       <c r="R3" t="n">
-        <v>7198189</v>
+        <v>7198250</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497183</v>
+        <v>121497206</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549164</v>
+        <v>548952</v>
       </c>
       <c r="R4" t="n">
-        <v>7198193</v>
+        <v>7198228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497204</v>
+        <v>121497191</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>74694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548901</v>
+        <v>549086</v>
       </c>
       <c r="R5" t="n">
-        <v>7198259</v>
+        <v>7198360</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497169</v>
+        <v>121497187</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549145</v>
+        <v>549143</v>
       </c>
       <c r="R6" t="n">
-        <v>7198071</v>
+        <v>7198250</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497194</v>
+        <v>121497161</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549039</v>
+        <v>549102</v>
       </c>
       <c r="R7" t="n">
-        <v>7198351</v>
+        <v>7197710</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497187</v>
+        <v>121497194</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549143</v>
+        <v>549039</v>
       </c>
       <c r="R8" t="n">
-        <v>7198250</v>
+        <v>7198351</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497186</v>
+        <v>121497165</v>
       </c>
       <c r="B9" t="n">
         <v>79686</v>
@@ -1499,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549143</v>
+        <v>549099</v>
       </c>
       <c r="R9" t="n">
-        <v>7198250</v>
+        <v>7197953</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497166</v>
+        <v>121497203</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1723,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549115</v>
+        <v>548894</v>
       </c>
       <c r="R11" t="n">
-        <v>7197960</v>
+        <v>7198284</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497191</v>
+        <v>121497167</v>
       </c>
       <c r="B12" t="n">
-        <v>74694</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1817,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549086</v>
+        <v>549130</v>
       </c>
       <c r="R12" t="n">
-        <v>7198360</v>
+        <v>7198017</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497209</v>
+        <v>121497208</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1952,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549014</v>
+        <v>548950</v>
       </c>
       <c r="R13" t="n">
-        <v>7198006</v>
+        <v>7198094</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497193</v>
+        <v>121497204</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549039</v>
+        <v>548901</v>
       </c>
       <c r="R14" t="n">
-        <v>7198351</v>
+        <v>7198259</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497177</v>
+        <v>121497205</v>
       </c>
       <c r="B15" t="n">
-        <v>79686</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,34 +2162,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549194</v>
+        <v>548901</v>
       </c>
       <c r="R15" t="n">
-        <v>7198164</v>
+        <v>7198259</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497179</v>
+        <v>121497207</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549168</v>
+        <v>548954</v>
       </c>
       <c r="R16" t="n">
-        <v>7198189</v>
+        <v>7198216</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2380,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497202</v>
+        <v>121497166</v>
       </c>
       <c r="B17" t="n">
         <v>78604</v>
@@ -2405,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548884</v>
+        <v>549115</v>
       </c>
       <c r="R17" t="n">
-        <v>7198316</v>
+        <v>7197960</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,7 +2492,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497207</v>
+        <v>121497171</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2513,7 +2528,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2522,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548954</v>
+        <v>549185</v>
       </c>
       <c r="R18" t="n">
-        <v>7198216</v>
+        <v>7198089</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497162</v>
+        <v>121497201</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>90996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,39 +2625,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549089</v>
+        <v>548884</v>
       </c>
       <c r="R19" t="n">
-        <v>7197751</v>
+        <v>7198317</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497206</v>
+        <v>121497184</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>79686</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2737,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2761,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548952</v>
+        <v>549161</v>
       </c>
       <c r="R20" t="n">
-        <v>7198228</v>
+        <v>7198220</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2786,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,7 +2833,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497174</v>
+        <v>121497183</v>
       </c>
       <c r="B21" t="n">
         <v>78604</v>
@@ -2863,10 +2873,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549183</v>
+        <v>549164</v>
       </c>
       <c r="R21" t="n">
-        <v>7198122</v>
+        <v>7198193</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497180</v>
+        <v>121497168</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>79686</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,38 +2961,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549163</v>
+        <v>549146</v>
       </c>
       <c r="R22" t="n">
-        <v>7198196</v>
+        <v>7198067</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,7 +3057,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497171</v>
+        <v>121497162</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -3096,10 +3102,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549185</v>
+        <v>549089</v>
       </c>
       <c r="R23" t="n">
-        <v>7198089</v>
+        <v>7197751</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3131,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497189</v>
+        <v>121497179</v>
       </c>
       <c r="B24" t="n">
-        <v>79686</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,21 +3190,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3208,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549139</v>
+        <v>549168</v>
       </c>
       <c r="R24" t="n">
-        <v>7198261</v>
+        <v>7198189</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3243,7 +3249,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3253,7 +3259,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497161</v>
+        <v>121497169</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>79714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,43 +3298,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549102</v>
+        <v>549145</v>
       </c>
       <c r="R25" t="n">
-        <v>7197710</v>
+        <v>7198071</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3360,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3370,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497176</v>
+        <v>121497170</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,21 +3414,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3437,10 +3438,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549196</v>
+        <v>549175</v>
       </c>
       <c r="R26" t="n">
-        <v>7198165</v>
+        <v>7198087</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3472,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3482,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3621,7 +3622,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497167</v>
+        <v>121497176</v>
       </c>
       <c r="B28" t="n">
         <v>78604</v>
@@ -3661,10 +3662,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549130</v>
+        <v>549196</v>
       </c>
       <c r="R28" t="n">
-        <v>7198017</v>
+        <v>7198165</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3696,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3706,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,7 +3734,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497203</v>
+        <v>121497185</v>
       </c>
       <c r="B29" t="n">
         <v>78604</v>
@@ -3773,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548894</v>
+        <v>549161</v>
       </c>
       <c r="R29" t="n">
-        <v>7198284</v>
+        <v>7198217</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3808,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3818,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3845,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497200</v>
+        <v>121497175</v>
       </c>
       <c r="B30" t="n">
-        <v>91150</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,25 +3858,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3885,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548885</v>
+        <v>549197</v>
       </c>
       <c r="R30" t="n">
-        <v>7198318</v>
+        <v>7198165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3920,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3930,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3957,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497172</v>
+        <v>121497174</v>
       </c>
       <c r="B31" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,39 +3974,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549180</v>
+        <v>549183</v>
       </c>
       <c r="R31" t="n">
-        <v>7198099</v>
+        <v>7198122</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4037,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4047,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497195</v>
+        <v>121497178</v>
       </c>
       <c r="B32" t="n">
-        <v>79686</v>
+        <v>79714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548975</v>
+        <v>549168</v>
       </c>
       <c r="R32" t="n">
-        <v>7198330</v>
+        <v>7198189</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4149,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497192</v>
+        <v>121497182</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4202,21 +4198,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4226,10 +4222,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549086</v>
+        <v>549164</v>
       </c>
       <c r="R33" t="n">
-        <v>7198360</v>
+        <v>7198194</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4261,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4271,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497208</v>
+        <v>121497195</v>
       </c>
       <c r="B34" t="n">
-        <v>57351</v>
+        <v>79686</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4314,39 +4310,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548950</v>
+        <v>548975</v>
       </c>
       <c r="R34" t="n">
-        <v>7198094</v>
+        <v>7198330</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4369,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4379,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497182</v>
+        <v>121497190</v>
       </c>
       <c r="B35" t="n">
-        <v>82388</v>
+        <v>79686</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4431,21 +4422,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4455,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549164</v>
+        <v>549134</v>
       </c>
       <c r="R35" t="n">
-        <v>7198194</v>
+        <v>7198295</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497205</v>
+        <v>121497163</v>
       </c>
       <c r="B36" t="n">
-        <v>57351</v>
+        <v>97049</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,43 +4530,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548901</v>
+        <v>549066</v>
       </c>
       <c r="R36" t="n">
-        <v>7198259</v>
+        <v>7197912</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4607,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4644,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497185</v>
+        <v>121497181</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4660,34 +4646,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549161</v>
+        <v>549164</v>
       </c>
       <c r="R37" t="n">
-        <v>7198217</v>
+        <v>7198195</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4719,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497163</v>
+        <v>121497189</v>
       </c>
       <c r="B38" t="n">
-        <v>97049</v>
+        <v>79686</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4768,25 +4759,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4796,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549066</v>
+        <v>549139</v>
       </c>
       <c r="R38" t="n">
-        <v>7197912</v>
+        <v>7198261</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4831,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4841,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497181</v>
+        <v>121497202</v>
       </c>
       <c r="B39" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4884,39 +4875,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549164</v>
+        <v>548884</v>
       </c>
       <c r="R39" t="n">
-        <v>7198195</v>
+        <v>7198316</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4948,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4958,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4985,7 +4971,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497184</v>
+        <v>121497177</v>
       </c>
       <c r="B40" t="n">
         <v>79686</v>
@@ -5025,10 +5011,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549161</v>
+        <v>549194</v>
       </c>
       <c r="R40" t="n">
-        <v>7198220</v>
+        <v>7198164</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5060,7 +5046,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5070,7 +5056,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497201</v>
+        <v>121497164</v>
       </c>
       <c r="B41" t="n">
-        <v>90996</v>
+        <v>79714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5109,25 +5095,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5137,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548884</v>
+        <v>549099</v>
       </c>
       <c r="R41" t="n">
-        <v>7198317</v>
+        <v>7197953</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5172,7 +5158,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5182,7 +5168,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,10 +5195,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497164</v>
+        <v>121497193</v>
       </c>
       <c r="B42" t="n">
-        <v>79714</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5221,38 +5207,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549099</v>
+        <v>549039</v>
       </c>
       <c r="R42" t="n">
-        <v>7197953</v>
+        <v>7198351</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5284,7 +5275,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5294,7 +5285,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5321,10 +5312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497170</v>
+        <v>121497192</v>
       </c>
       <c r="B43" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5337,21 +5328,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5361,10 +5352,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549175</v>
+        <v>549086</v>
       </c>
       <c r="R43" t="n">
-        <v>7198087</v>
+        <v>7198360</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5396,7 +5387,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5406,7 +5397,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,10 +5424,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497168</v>
+        <v>121497172</v>
       </c>
       <c r="B44" t="n">
-        <v>79686</v>
+        <v>57351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5449,34 +5440,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549146</v>
+        <v>549180</v>
       </c>
       <c r="R44" t="n">
-        <v>7198067</v>
+        <v>7198099</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5541,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497165</v>
+        <v>121497200</v>
       </c>
       <c r="B45" t="n">
-        <v>79686</v>
+        <v>91150</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5553,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5581,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549099</v>
+        <v>548885</v>
       </c>
       <c r="R45" t="n">
-        <v>7197953</v>
+        <v>7198318</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5653,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497175</v>
+        <v>121497180</v>
       </c>
       <c r="B46" t="n">
-        <v>90728</v>
+        <v>57504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,34 +5669,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549197</v>
+        <v>549163</v>
       </c>
       <c r="R46" t="n">
-        <v>7198165</v>
+        <v>7198196</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497209</v>
+        <v>121497192</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549014</v>
+        <v>549086</v>
       </c>
       <c r="R2" t="n">
-        <v>7198006</v>
+        <v>7198360</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497186</v>
+        <v>121497167</v>
       </c>
       <c r="B3" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549143</v>
+        <v>549130</v>
       </c>
       <c r="R3" t="n">
-        <v>7198250</v>
+        <v>7198017</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497206</v>
+        <v>121497169</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548952</v>
+        <v>549145</v>
       </c>
       <c r="R4" t="n">
-        <v>7198228</v>
+        <v>7198071</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497191</v>
+        <v>121497183</v>
       </c>
       <c r="B5" t="n">
-        <v>74694</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549086</v>
+        <v>549164</v>
       </c>
       <c r="R5" t="n">
-        <v>7198360</v>
+        <v>7198193</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497187</v>
+        <v>121497162</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549143</v>
+        <v>549089</v>
       </c>
       <c r="R6" t="n">
-        <v>7198250</v>
+        <v>7197751</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497161</v>
+        <v>121497189</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549102</v>
+        <v>549139</v>
       </c>
       <c r="R7" t="n">
-        <v>7197710</v>
+        <v>7198261</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497194</v>
+        <v>121497172</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549039</v>
+        <v>549180</v>
       </c>
       <c r="R8" t="n">
-        <v>7198351</v>
+        <v>7198099</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497165</v>
+        <v>121497203</v>
       </c>
       <c r="B9" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549099</v>
+        <v>548894</v>
       </c>
       <c r="R9" t="n">
-        <v>7197953</v>
+        <v>7198284</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497188</v>
+        <v>121497206</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549143</v>
+        <v>548952</v>
       </c>
       <c r="R10" t="n">
-        <v>7198251</v>
+        <v>7198228</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497203</v>
+        <v>121497185</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548894</v>
+        <v>549161</v>
       </c>
       <c r="R11" t="n">
-        <v>7198284</v>
+        <v>7198217</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497167</v>
+        <v>121497168</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549130</v>
+        <v>549146</v>
       </c>
       <c r="R12" t="n">
-        <v>7198017</v>
+        <v>7198067</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497208</v>
+        <v>121497179</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,39 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548950</v>
+        <v>549168</v>
       </c>
       <c r="R13" t="n">
-        <v>7198094</v>
+        <v>7198189</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497204</v>
+        <v>121497194</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548901</v>
+        <v>549039</v>
       </c>
       <c r="R14" t="n">
-        <v>7198259</v>
+        <v>7198351</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497205</v>
+        <v>121497173</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>79717</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,43 +2153,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548901</v>
+        <v>549182</v>
       </c>
       <c r="R15" t="n">
-        <v>7198259</v>
+        <v>7198123</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497207</v>
+        <v>121497177</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,39 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548954</v>
+        <v>549194</v>
       </c>
       <c r="R16" t="n">
-        <v>7198216</v>
+        <v>7198164</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497166</v>
+        <v>121497188</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549115</v>
+        <v>549143</v>
       </c>
       <c r="R17" t="n">
-        <v>7197960</v>
+        <v>7198251</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497171</v>
+        <v>121497161</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549185</v>
+        <v>549102</v>
       </c>
       <c r="R18" t="n">
-        <v>7198089</v>
+        <v>7197710</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497201</v>
+        <v>121497171</v>
       </c>
       <c r="B19" t="n">
-        <v>90996</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,34 +2610,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548884</v>
+        <v>549185</v>
       </c>
       <c r="R19" t="n">
-        <v>7198317</v>
+        <v>7198089</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497184</v>
+        <v>121497187</v>
       </c>
       <c r="B20" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2761,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549161</v>
+        <v>549143</v>
       </c>
       <c r="R20" t="n">
-        <v>7198220</v>
+        <v>7198250</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2796,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497183</v>
+        <v>121497191</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>74697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,25 +2835,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549164</v>
+        <v>549086</v>
       </c>
       <c r="R21" t="n">
-        <v>7198193</v>
+        <v>7198360</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2908,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497168</v>
+        <v>121497202</v>
       </c>
       <c r="B22" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549146</v>
+        <v>548884</v>
       </c>
       <c r="R22" t="n">
-        <v>7198067</v>
+        <v>7198316</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3020,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497162</v>
+        <v>121497180</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,27 +3063,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3102,10 +3091,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549089</v>
+        <v>549163</v>
       </c>
       <c r="R23" t="n">
-        <v>7197751</v>
+        <v>7198196</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3137,7 +3126,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3136,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497179</v>
+        <v>121497175</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,21 +3179,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3214,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549168</v>
+        <v>549197</v>
       </c>
       <c r="R24" t="n">
-        <v>7198189</v>
+        <v>7198165</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3249,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3259,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497169</v>
+        <v>121497209</v>
       </c>
       <c r="B25" t="n">
-        <v>79714</v>
+        <v>57354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,38 +3287,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549145</v>
+        <v>549014</v>
       </c>
       <c r="R25" t="n">
-        <v>7198071</v>
+        <v>7198006</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3361,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497170</v>
+        <v>121497207</v>
       </c>
       <c r="B26" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,34 +3408,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549175</v>
+        <v>548954</v>
       </c>
       <c r="R26" t="n">
-        <v>7198087</v>
+        <v>7198216</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3473,7 +3472,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3482,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497173</v>
+        <v>121497182</v>
       </c>
       <c r="B27" t="n">
-        <v>79714</v>
+        <v>82391</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,25 +3521,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3550,10 +3549,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549182</v>
+        <v>549164</v>
       </c>
       <c r="R27" t="n">
-        <v>7198123</v>
+        <v>7198194</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3585,7 +3584,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3594,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,7 +3624,7 @@
         <v>121497176</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3734,10 +3733,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497185</v>
+        <v>121497174</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3774,10 +3773,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549161</v>
+        <v>549183</v>
       </c>
       <c r="R29" t="n">
-        <v>7198217</v>
+        <v>7198122</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3808,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3818,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3845,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497175</v>
+        <v>121497181</v>
       </c>
       <c r="B30" t="n">
-        <v>90728</v>
+        <v>57370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,34 +3861,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549197</v>
+        <v>549164</v>
       </c>
       <c r="R30" t="n">
-        <v>7198165</v>
+        <v>7198195</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497174</v>
+        <v>121497178</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3974,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549183</v>
+        <v>549168</v>
       </c>
       <c r="R31" t="n">
-        <v>7198122</v>
+        <v>7198189</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4037,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4074,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497178</v>
+        <v>121497163</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>97052</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,21 +4090,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4110,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549168</v>
+        <v>549066</v>
       </c>
       <c r="R32" t="n">
-        <v>7198189</v>
+        <v>7197912</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4149,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4159,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497182</v>
+        <v>121497186</v>
       </c>
       <c r="B33" t="n">
-        <v>82388</v>
+        <v>79689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,21 +4202,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4222,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549164</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>7198194</v>
+        <v>7198250</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4261,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4271,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4298,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497195</v>
+        <v>121497208</v>
       </c>
       <c r="B34" t="n">
-        <v>79686</v>
+        <v>57354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,34 +4314,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548975</v>
+        <v>548950</v>
       </c>
       <c r="R34" t="n">
-        <v>7198330</v>
+        <v>7198094</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,10 +4415,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497190</v>
+        <v>121497195</v>
       </c>
       <c r="B35" t="n">
-        <v>79686</v>
+        <v>79689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549134</v>
+        <v>548975</v>
       </c>
       <c r="R35" t="n">
-        <v>7198295</v>
+        <v>7198330</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497163</v>
+        <v>121497201</v>
       </c>
       <c r="B36" t="n">
-        <v>97049</v>
+        <v>90999</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4530,25 +4539,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4558,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549066</v>
+        <v>548884</v>
       </c>
       <c r="R36" t="n">
-        <v>7197912</v>
+        <v>7198317</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4593,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497181</v>
+        <v>121497190</v>
       </c>
       <c r="B37" t="n">
-        <v>57367</v>
+        <v>79689</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,39 +4655,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549164</v>
+        <v>549134</v>
       </c>
       <c r="R37" t="n">
-        <v>7198195</v>
+        <v>7198295</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497189</v>
+        <v>121497165</v>
       </c>
       <c r="B38" t="n">
-        <v>79686</v>
+        <v>79689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,10 +4791,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549139</v>
+        <v>549099</v>
       </c>
       <c r="R38" t="n">
-        <v>7198261</v>
+        <v>7197953</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4836,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497202</v>
+        <v>121497193</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,34 +4879,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548884</v>
+        <v>549039</v>
       </c>
       <c r="R39" t="n">
-        <v>7198316</v>
+        <v>7198351</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4943,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4953,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4971,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497177</v>
+        <v>121497200</v>
       </c>
       <c r="B40" t="n">
-        <v>79686</v>
+        <v>91153</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4983,25 +4992,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5011,10 +5020,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549194</v>
+        <v>548885</v>
       </c>
       <c r="R40" t="n">
-        <v>7198164</v>
+        <v>7198318</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5046,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5056,7 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,10 +5092,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497164</v>
+        <v>121497166</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>78607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5095,25 +5104,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5123,10 +5132,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549099</v>
+        <v>549115</v>
       </c>
       <c r="R41" t="n">
-        <v>7197953</v>
+        <v>7197960</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5158,7 +5167,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5168,7 +5177,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497193</v>
+        <v>121497170</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5211,39 +5220,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549039</v>
+        <v>549175</v>
       </c>
       <c r="R42" t="n">
-        <v>7198351</v>
+        <v>7198087</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5275,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5285,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5312,10 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497192</v>
+        <v>121497184</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>79689</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5328,21 +5332,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5352,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549086</v>
+        <v>549161</v>
       </c>
       <c r="R43" t="n">
-        <v>7198360</v>
+        <v>7198220</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5387,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5424,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497172</v>
+        <v>121497204</v>
       </c>
       <c r="B44" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,39 +5444,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549180</v>
+        <v>548901</v>
       </c>
       <c r="R44" t="n">
-        <v>7198099</v>
+        <v>7198259</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5504,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5514,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5541,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497200</v>
+        <v>121497205</v>
       </c>
       <c r="B45" t="n">
-        <v>91150</v>
+        <v>57354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5553,38 +5552,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548885</v>
+        <v>548901</v>
       </c>
       <c r="R45" t="n">
-        <v>7198318</v>
+        <v>7198259</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5616,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497180</v>
+        <v>121497164</v>
       </c>
       <c r="B46" t="n">
-        <v>57504</v>
+        <v>79717</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5665,42 +5669,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549163</v>
+        <v>549099</v>
       </c>
       <c r="R46" t="n">
-        <v>7198196</v>
+        <v>7197953</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497192</v>
+        <v>121497188</v>
       </c>
       <c r="B2" t="n">
         <v>78607</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549086</v>
+        <v>549143</v>
       </c>
       <c r="R2" t="n">
-        <v>7198360</v>
+        <v>7198251</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497167</v>
+        <v>121497205</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549130</v>
+        <v>548901</v>
       </c>
       <c r="R3" t="n">
-        <v>7198017</v>
+        <v>7198259</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497169</v>
+        <v>121497173</v>
       </c>
       <c r="B4" t="n">
         <v>79717</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549145</v>
+        <v>549182</v>
       </c>
       <c r="R4" t="n">
-        <v>7198071</v>
+        <v>7198123</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497183</v>
+        <v>121497180</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549164</v>
+        <v>549163</v>
       </c>
       <c r="R5" t="n">
-        <v>7198193</v>
+        <v>7198196</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497162</v>
+        <v>121497201</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>90999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549089</v>
+        <v>548884</v>
       </c>
       <c r="R6" t="n">
-        <v>7197751</v>
+        <v>7198317</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497189</v>
+        <v>121497209</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1260,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549139</v>
+        <v>549014</v>
       </c>
       <c r="R7" t="n">
-        <v>7198261</v>
+        <v>7198006</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497172</v>
+        <v>121497181</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1388,7 +1397,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1397,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549180</v>
+        <v>549164</v>
       </c>
       <c r="R8" t="n">
-        <v>7198099</v>
+        <v>7198195</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497203</v>
+        <v>121497161</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548894</v>
+        <v>549102</v>
       </c>
       <c r="R9" t="n">
-        <v>7198284</v>
+        <v>7197710</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497206</v>
+        <v>121497208</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1611,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548952</v>
+        <v>548950</v>
       </c>
       <c r="R10" t="n">
-        <v>7198228</v>
+        <v>7198094</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497185</v>
+        <v>121497191</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>74697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1724,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549161</v>
+        <v>549086</v>
       </c>
       <c r="R11" t="n">
-        <v>7198217</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497168</v>
+        <v>121497166</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1840,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549146</v>
+        <v>549115</v>
       </c>
       <c r="R12" t="n">
-        <v>7198067</v>
+        <v>7197960</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497179</v>
+        <v>121497172</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,34 +1952,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549168</v>
+        <v>549180</v>
       </c>
       <c r="R13" t="n">
-        <v>7198189</v>
+        <v>7198099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497194</v>
+        <v>121497175</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2069,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549039</v>
+        <v>549197</v>
       </c>
       <c r="R14" t="n">
-        <v>7198351</v>
+        <v>7198165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497173</v>
+        <v>121497183</v>
       </c>
       <c r="B15" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,25 +2177,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549182</v>
+        <v>549164</v>
       </c>
       <c r="R15" t="n">
-        <v>7198123</v>
+        <v>7198193</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497177</v>
+        <v>121497207</v>
       </c>
       <c r="B16" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,34 +2293,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549194</v>
+        <v>548954</v>
       </c>
       <c r="R16" t="n">
-        <v>7198164</v>
+        <v>7198216</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497188</v>
+        <v>121497165</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549143</v>
+        <v>549099</v>
       </c>
       <c r="R17" t="n">
-        <v>7198251</v>
+        <v>7197953</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497161</v>
+        <v>121497202</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,39 +2522,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549102</v>
+        <v>548884</v>
       </c>
       <c r="R18" t="n">
-        <v>7197710</v>
+        <v>7198316</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,7 +2618,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497171</v>
+        <v>121497193</v>
       </c>
       <c r="B19" t="n">
         <v>57354</v>
@@ -2630,7 +2654,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2639,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549185</v>
+        <v>549039</v>
       </c>
       <c r="R19" t="n">
-        <v>7198089</v>
+        <v>7198351</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497187</v>
+        <v>121497206</v>
       </c>
       <c r="B20" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2751,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549143</v>
+        <v>548952</v>
       </c>
       <c r="R20" t="n">
-        <v>7198250</v>
+        <v>7198228</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2786,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497191</v>
+        <v>121497163</v>
       </c>
       <c r="B21" t="n">
-        <v>74697</v>
+        <v>97052</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,21 +2863,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549086</v>
+        <v>549066</v>
       </c>
       <c r="R21" t="n">
-        <v>7198360</v>
+        <v>7197912</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497202</v>
+        <v>121497200</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>91153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,25 +2971,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2999,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548884</v>
+        <v>548885</v>
       </c>
       <c r="R22" t="n">
-        <v>7198316</v>
+        <v>7198318</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497180</v>
+        <v>121497185</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,38 +3087,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549163</v>
+        <v>549161</v>
       </c>
       <c r="R23" t="n">
-        <v>7198196</v>
+        <v>7198217</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,10 +3183,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497175</v>
+        <v>121497176</v>
       </c>
       <c r="B24" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,21 +3199,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,7 +3223,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549197</v>
+        <v>549196</v>
       </c>
       <c r="R24" t="n">
         <v>7198165</v>
@@ -3238,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,10 +3295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497209</v>
+        <v>121497177</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,39 +3311,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549014</v>
+        <v>549194</v>
       </c>
       <c r="R25" t="n">
-        <v>7198006</v>
+        <v>7198164</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3355,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497207</v>
+        <v>121497194</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,39 +3423,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548954</v>
+        <v>549039</v>
       </c>
       <c r="R26" t="n">
-        <v>7198216</v>
+        <v>7198351</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3472,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3482,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497182</v>
+        <v>121497170</v>
       </c>
       <c r="B27" t="n">
-        <v>82391</v>
+        <v>79688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3549,10 +3559,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549164</v>
+        <v>549175</v>
       </c>
       <c r="R27" t="n">
-        <v>7198194</v>
+        <v>7198087</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3584,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3594,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,10 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497176</v>
+        <v>121497162</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3637,34 +3647,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549196</v>
+        <v>549089</v>
       </c>
       <c r="R28" t="n">
-        <v>7198165</v>
+        <v>7197751</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3696,7 +3711,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3706,7 +3721,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3845,10 +3860,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497181</v>
+        <v>121497178</v>
       </c>
       <c r="B30" t="n">
-        <v>57370</v>
+        <v>79717</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,43 +3872,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549164</v>
+        <v>549168</v>
       </c>
       <c r="R30" t="n">
-        <v>7198195</v>
+        <v>7198189</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3925,7 +3935,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3945,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,10 +3972,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497178</v>
+        <v>121497171</v>
       </c>
       <c r="B31" t="n">
-        <v>79717</v>
+        <v>57354</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,38 +3984,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549168</v>
+        <v>549185</v>
       </c>
       <c r="R31" t="n">
-        <v>7198189</v>
+        <v>7198089</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4037,7 +4052,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4047,7 +4062,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,10 +4089,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497163</v>
+        <v>121497182</v>
       </c>
       <c r="B32" t="n">
-        <v>97052</v>
+        <v>82391</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,25 +4101,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4129,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549066</v>
+        <v>549164</v>
       </c>
       <c r="R32" t="n">
-        <v>7197912</v>
+        <v>7198194</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4149,7 +4164,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4174,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,7 +4201,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497186</v>
+        <v>121497184</v>
       </c>
       <c r="B33" t="n">
         <v>79689</v>
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549161</v>
       </c>
       <c r="R33" t="n">
-        <v>7198250</v>
+        <v>7198220</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4261,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4271,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,10 +4313,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497208</v>
+        <v>121497192</v>
       </c>
       <c r="B34" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4314,39 +4329,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548950</v>
+        <v>549086</v>
       </c>
       <c r="R34" t="n">
-        <v>7198094</v>
+        <v>7198360</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4388,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4398,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,7 +4425,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497195</v>
+        <v>121497190</v>
       </c>
       <c r="B35" t="n">
         <v>79689</v>
@@ -4455,10 +4465,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548975</v>
+        <v>549134</v>
       </c>
       <c r="R35" t="n">
-        <v>7198330</v>
+        <v>7198295</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4500,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4510,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497201</v>
+        <v>121497168</v>
       </c>
       <c r="B36" t="n">
-        <v>90999</v>
+        <v>79689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4543,21 +4553,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4567,10 +4577,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548884</v>
+        <v>549146</v>
       </c>
       <c r="R36" t="n">
-        <v>7198317</v>
+        <v>7198067</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,7 +4649,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497190</v>
+        <v>121497195</v>
       </c>
       <c r="B37" t="n">
         <v>79689</v>
@@ -4679,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549134</v>
+        <v>548975</v>
       </c>
       <c r="R37" t="n">
-        <v>7198295</v>
+        <v>7198330</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4714,7 +4724,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4724,7 +4734,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497165</v>
+        <v>121497169</v>
       </c>
       <c r="B38" t="n">
-        <v>79689</v>
+        <v>79717</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,25 +4773,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4791,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549099</v>
+        <v>549145</v>
       </c>
       <c r="R38" t="n">
-        <v>7197953</v>
+        <v>7198071</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4826,7 +4836,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4836,7 +4846,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,10 +4873,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497193</v>
+        <v>121497164</v>
       </c>
       <c r="B39" t="n">
-        <v>57354</v>
+        <v>79717</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,43 +4885,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549039</v>
+        <v>549099</v>
       </c>
       <c r="R39" t="n">
-        <v>7198351</v>
+        <v>7197953</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4943,7 +4948,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4958,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,10 +4985,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497200</v>
+        <v>121497186</v>
       </c>
       <c r="B40" t="n">
-        <v>91153</v>
+        <v>79689</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,25 +4997,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548885</v>
+        <v>549143</v>
       </c>
       <c r="R40" t="n">
-        <v>7198318</v>
+        <v>7198250</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5055,7 +5060,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +5070,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,10 +5097,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497166</v>
+        <v>121497189</v>
       </c>
       <c r="B41" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,21 +5113,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5132,10 +5137,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549115</v>
+        <v>549139</v>
       </c>
       <c r="R41" t="n">
-        <v>7197960</v>
+        <v>7198261</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5167,7 +5172,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,7 +5182,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,7 +5209,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497170</v>
+        <v>121497187</v>
       </c>
       <c r="B42" t="n">
         <v>79688</v>
@@ -5244,10 +5249,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549175</v>
+        <v>549143</v>
       </c>
       <c r="R42" t="n">
-        <v>7198087</v>
+        <v>7198250</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5279,7 +5284,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5294,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,10 +5321,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497184</v>
+        <v>121497167</v>
       </c>
       <c r="B43" t="n">
-        <v>79689</v>
+        <v>78607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,21 +5337,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5356,10 +5361,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549161</v>
+        <v>549130</v>
       </c>
       <c r="R43" t="n">
-        <v>7198220</v>
+        <v>7198017</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5396,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5406,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,7 +5433,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497204</v>
+        <v>121497179</v>
       </c>
       <c r="B44" t="n">
         <v>78607</v>
@@ -5468,10 +5473,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548901</v>
+        <v>549168</v>
       </c>
       <c r="R44" t="n">
-        <v>7198259</v>
+        <v>7198189</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5508,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5518,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497205</v>
+        <v>121497203</v>
       </c>
       <c r="B45" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5556,39 +5561,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548901</v>
+        <v>548894</v>
       </c>
       <c r="R45" t="n">
-        <v>7198259</v>
+        <v>7198284</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497164</v>
+        <v>121497204</v>
       </c>
       <c r="B46" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5669,25 +5669,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549099</v>
+        <v>548901</v>
       </c>
       <c r="R46" t="n">
-        <v>7197953</v>
+        <v>7198259</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497209</v>
+        <v>121497181</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549014</v>
+        <v>549164</v>
       </c>
       <c r="R7" t="n">
-        <v>7198006</v>
+        <v>7198195</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497181</v>
+        <v>121497209</v>
       </c>
       <c r="B8" t="n">
-        <v>57370</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549164</v>
+        <v>549014</v>
       </c>
       <c r="R8" t="n">
-        <v>7198195</v>
+        <v>7198006</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497205</v>
+        <v>121497173</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>79717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548901</v>
+        <v>549182</v>
       </c>
       <c r="R3" t="n">
-        <v>7198259</v>
+        <v>7198123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497173</v>
+        <v>121497205</v>
       </c>
       <c r="B4" t="n">
-        <v>79717</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549182</v>
+        <v>548901</v>
       </c>
       <c r="R4" t="n">
-        <v>7198123</v>
+        <v>7198259</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497165</v>
+        <v>121497193</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,34 +2410,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549099</v>
+        <v>549039</v>
       </c>
       <c r="R17" t="n">
-        <v>7197953</v>
+        <v>7198351</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497193</v>
+        <v>121497165</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>79689</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,39 +2639,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549039</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>7198351</v>
+        <v>7197953</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497206</v>
+        <v>121497163</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548952</v>
+        <v>549066</v>
       </c>
       <c r="R20" t="n">
-        <v>7198228</v>
+        <v>7197912</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497163</v>
+        <v>121497206</v>
       </c>
       <c r="B21" t="n">
-        <v>97052</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,25 +2859,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549066</v>
+        <v>548952</v>
       </c>
       <c r="R21" t="n">
-        <v>7197912</v>
+        <v>7198228</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497188</v>
+        <v>121497203</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549143</v>
+        <v>548894</v>
       </c>
       <c r="R2" t="n">
-        <v>7198251</v>
+        <v>7198284</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497173</v>
+        <v>121497178</v>
       </c>
       <c r="B3" t="n">
-        <v>79717</v>
+        <v>79718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549182</v>
+        <v>549168</v>
       </c>
       <c r="R3" t="n">
-        <v>7198123</v>
+        <v>7198189</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497205</v>
+        <v>121497187</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548901</v>
+        <v>549143</v>
       </c>
       <c r="R4" t="n">
-        <v>7198259</v>
+        <v>7198250</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497180</v>
+        <v>121497172</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,26 +1027,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549163</v>
+        <v>549180</v>
       </c>
       <c r="R5" t="n">
-        <v>7198196</v>
+        <v>7198099</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497201</v>
+        <v>121497162</v>
       </c>
       <c r="B6" t="n">
-        <v>90999</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548884</v>
+        <v>549089</v>
       </c>
       <c r="R6" t="n">
-        <v>7198317</v>
+        <v>7197751</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497181</v>
+        <v>121497185</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549164</v>
+        <v>549161</v>
       </c>
       <c r="R7" t="n">
-        <v>7198195</v>
+        <v>7198217</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497209</v>
+        <v>121497177</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549014</v>
+        <v>549194</v>
       </c>
       <c r="R8" t="n">
-        <v>7198006</v>
+        <v>7198164</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497161</v>
+        <v>121497176</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549102</v>
+        <v>549196</v>
       </c>
       <c r="R9" t="n">
-        <v>7197710</v>
+        <v>7198165</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497208</v>
+        <v>121497167</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548950</v>
+        <v>549130</v>
       </c>
       <c r="R10" t="n">
-        <v>7198094</v>
+        <v>7198017</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497191</v>
+        <v>121497175</v>
       </c>
       <c r="B11" t="n">
-        <v>74697</v>
+        <v>90737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549086</v>
+        <v>549197</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198165</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497166</v>
+        <v>121497183</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549115</v>
+        <v>549164</v>
       </c>
       <c r="R12" t="n">
-        <v>7197960</v>
+        <v>7198193</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497172</v>
+        <v>121497180</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,27 +1933,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1981,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549180</v>
+        <v>549163</v>
       </c>
       <c r="R13" t="n">
-        <v>7198099</v>
+        <v>7198196</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497175</v>
+        <v>121497182</v>
       </c>
       <c r="B14" t="n">
-        <v>90731</v>
+        <v>82392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549197</v>
+        <v>549164</v>
       </c>
       <c r="R14" t="n">
-        <v>7198165</v>
+        <v>7198194</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497183</v>
+        <v>121497204</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2205,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549164</v>
+        <v>548901</v>
       </c>
       <c r="R15" t="n">
-        <v>7198193</v>
+        <v>7198259</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497207</v>
+        <v>121497201</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>91005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,39 +2273,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548954</v>
+        <v>548884</v>
       </c>
       <c r="R16" t="n">
-        <v>7198216</v>
+        <v>7198317</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497193</v>
+        <v>121497208</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,7 +2405,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549039</v>
+        <v>548950</v>
       </c>
       <c r="R17" t="n">
-        <v>7198351</v>
+        <v>7198094</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2449,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2459,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497202</v>
+        <v>121497200</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>91159</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,25 +2498,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548884</v>
+        <v>548885</v>
       </c>
       <c r="R18" t="n">
-        <v>7198316</v>
+        <v>7198318</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2623,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497165</v>
+        <v>121497192</v>
       </c>
       <c r="B19" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2614,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549086</v>
       </c>
       <c r="R19" t="n">
-        <v>7197953</v>
+        <v>7198360</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2673,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2683,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497163</v>
+        <v>121497179</v>
       </c>
       <c r="B20" t="n">
-        <v>97052</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,25 +2722,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2775,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549066</v>
+        <v>549168</v>
       </c>
       <c r="R20" t="n">
-        <v>7197912</v>
+        <v>7198189</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2785,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2795,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497206</v>
+        <v>121497163</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>97058</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548952</v>
+        <v>549066</v>
       </c>
       <c r="R21" t="n">
-        <v>7198228</v>
+        <v>7197912</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2907,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497200</v>
+        <v>121497166</v>
       </c>
       <c r="B22" t="n">
-        <v>91153</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,25 +2946,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +2974,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548885</v>
+        <v>549115</v>
       </c>
       <c r="R22" t="n">
-        <v>7198318</v>
+        <v>7197960</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,7 +3009,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3019,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497185</v>
+        <v>121497181</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,34 +3062,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549161</v>
+        <v>549164</v>
       </c>
       <c r="R23" t="n">
-        <v>7198217</v>
+        <v>7198195</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +3126,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3136,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497176</v>
+        <v>121497173</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,25 +3175,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3223,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549196</v>
+        <v>549182</v>
       </c>
       <c r="R24" t="n">
-        <v>7198165</v>
+        <v>7198123</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3258,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497177</v>
+        <v>121497190</v>
       </c>
       <c r="B25" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,10 +3315,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549194</v>
+        <v>549134</v>
       </c>
       <c r="R25" t="n">
-        <v>7198164</v>
+        <v>7198295</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3370,7 +3350,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3360,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,10 +3387,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497194</v>
+        <v>121497209</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,34 +3403,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549039</v>
+        <v>549014</v>
       </c>
       <c r="R26" t="n">
-        <v>7198351</v>
+        <v>7198006</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3482,7 +3467,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3477,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,10 +3504,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497170</v>
+        <v>121497205</v>
       </c>
       <c r="B27" t="n">
-        <v>79688</v>
+        <v>57355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,34 +3520,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549175</v>
+        <v>548901</v>
       </c>
       <c r="R27" t="n">
-        <v>7198087</v>
+        <v>7198259</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3594,7 +3584,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3594,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,10 +3621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497162</v>
+        <v>121497161</v>
       </c>
       <c r="B28" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549089</v>
+        <v>549102</v>
       </c>
       <c r="R28" t="n">
-        <v>7197751</v>
+        <v>7197710</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3748,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497174</v>
+        <v>121497193</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,34 +3754,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549183</v>
+        <v>549039</v>
       </c>
       <c r="R29" t="n">
-        <v>7198122</v>
+        <v>7198351</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3823,7 +3818,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3833,7 +3828,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497178</v>
+        <v>121497184</v>
       </c>
       <c r="B30" t="n">
-        <v>79717</v>
+        <v>79690</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,25 +3867,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549168</v>
+        <v>549161</v>
       </c>
       <c r="R30" t="n">
-        <v>7198189</v>
+        <v>7198220</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3945,7 +3940,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497171</v>
+        <v>121497206</v>
       </c>
       <c r="B31" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,39 +3983,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549185</v>
+        <v>548952</v>
       </c>
       <c r="R31" t="n">
-        <v>7198089</v>
+        <v>7198228</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4052,7 +4042,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4062,7 +4052,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,10 +4079,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497182</v>
+        <v>121497191</v>
       </c>
       <c r="B32" t="n">
-        <v>82391</v>
+        <v>74698</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4101,25 +4091,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4129,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549164</v>
+        <v>549086</v>
       </c>
       <c r="R32" t="n">
-        <v>7198194</v>
+        <v>7198360</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4164,7 +4154,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4174,7 +4164,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4201,10 +4191,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497184</v>
+        <v>121497168</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4241,10 +4231,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549161</v>
+        <v>549146</v>
       </c>
       <c r="R33" t="n">
-        <v>7198220</v>
+        <v>7198067</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4276,7 +4266,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4276,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4303,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497192</v>
+        <v>121497202</v>
       </c>
       <c r="B34" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,10 +4343,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549086</v>
+        <v>548884</v>
       </c>
       <c r="R34" t="n">
-        <v>7198360</v>
+        <v>7198316</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4388,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4398,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4425,7 +4415,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497190</v>
+        <v>121497170</v>
       </c>
       <c r="B35" t="n">
         <v>79689</v>
@@ -4441,21 +4431,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4465,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549134</v>
+        <v>549175</v>
       </c>
       <c r="R35" t="n">
-        <v>7198295</v>
+        <v>7198087</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4500,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4510,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497168</v>
+        <v>121497186</v>
       </c>
       <c r="B36" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4577,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549146</v>
+        <v>549143</v>
       </c>
       <c r="R36" t="n">
-        <v>7198067</v>
+        <v>7198250</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4612,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497195</v>
+        <v>121497189</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4689,10 +4679,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548975</v>
+        <v>549139</v>
       </c>
       <c r="R37" t="n">
-        <v>7198330</v>
+        <v>7198261</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4724,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4734,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,7 +4754,7 @@
         <v>121497169</v>
       </c>
       <c r="B38" t="n">
-        <v>79717</v>
+        <v>79718</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4873,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497164</v>
+        <v>121497188</v>
       </c>
       <c r="B39" t="n">
-        <v>79717</v>
+        <v>78608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4885,25 +4875,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4913,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549099</v>
+        <v>549143</v>
       </c>
       <c r="R39" t="n">
-        <v>7197953</v>
+        <v>7198251</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4948,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4958,7 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4985,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497186</v>
+        <v>121497174</v>
       </c>
       <c r="B40" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5001,21 +4991,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5025,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549143</v>
+        <v>549183</v>
       </c>
       <c r="R40" t="n">
-        <v>7198250</v>
+        <v>7198122</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5060,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5070,7 +5060,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497189</v>
+        <v>121497171</v>
       </c>
       <c r="B41" t="n">
-        <v>79689</v>
+        <v>57355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5113,34 +5103,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549139</v>
+        <v>549185</v>
       </c>
       <c r="R41" t="n">
-        <v>7198261</v>
+        <v>7198089</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5172,7 +5167,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5182,7 +5177,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497187</v>
+        <v>121497165</v>
       </c>
       <c r="B42" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5225,21 +5220,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5249,10 +5244,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549143</v>
+        <v>549099</v>
       </c>
       <c r="R42" t="n">
-        <v>7198250</v>
+        <v>7197953</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5284,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5294,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5321,10 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497167</v>
+        <v>121497194</v>
       </c>
       <c r="B43" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549130</v>
+        <v>549039</v>
       </c>
       <c r="R43" t="n">
-        <v>7198017</v>
+        <v>7198351</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5396,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5406,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497179</v>
+        <v>121497207</v>
       </c>
       <c r="B44" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5449,34 +5444,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549168</v>
+        <v>548954</v>
       </c>
       <c r="R44" t="n">
-        <v>7198189</v>
+        <v>7198216</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497203</v>
+        <v>121497195</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548894</v>
+        <v>548975</v>
       </c>
       <c r="R45" t="n">
-        <v>7198284</v>
+        <v>7198330</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497204</v>
+        <v>121497164</v>
       </c>
       <c r="B46" t="n">
-        <v>78607</v>
+        <v>79718</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5669,25 +5669,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548901</v>
+        <v>549099</v>
       </c>
       <c r="R46" t="n">
-        <v>7198259</v>
+        <v>7197953</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497203</v>
+        <v>121497173</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>79719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548894</v>
+        <v>549182</v>
       </c>
       <c r="R2" t="n">
-        <v>7198284</v>
+        <v>7198123</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497178</v>
+        <v>121497176</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549168</v>
+        <v>549196</v>
       </c>
       <c r="R3" t="n">
-        <v>7198189</v>
+        <v>7198165</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497187</v>
+        <v>121497169</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>79719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549143</v>
+        <v>549145</v>
       </c>
       <c r="R4" t="n">
-        <v>7198250</v>
+        <v>7198071</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497172</v>
+        <v>121497203</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549180</v>
+        <v>548894</v>
       </c>
       <c r="R5" t="n">
-        <v>7198099</v>
+        <v>7198284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497162</v>
+        <v>121497204</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549089</v>
+        <v>548901</v>
       </c>
       <c r="R6" t="n">
-        <v>7197751</v>
+        <v>7198259</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497185</v>
+        <v>121497200</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>91160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549161</v>
+        <v>548885</v>
       </c>
       <c r="R7" t="n">
-        <v>7198217</v>
+        <v>7198318</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497177</v>
+        <v>121497175</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549194</v>
+        <v>549197</v>
       </c>
       <c r="R8" t="n">
-        <v>7198164</v>
+        <v>7198165</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497176</v>
+        <v>121497206</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549196</v>
+        <v>548952</v>
       </c>
       <c r="R9" t="n">
-        <v>7198165</v>
+        <v>7198228</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497167</v>
+        <v>121497188</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549130</v>
+        <v>549143</v>
       </c>
       <c r="R10" t="n">
-        <v>7198017</v>
+        <v>7198251</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497175</v>
+        <v>121497183</v>
       </c>
       <c r="B11" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549197</v>
+        <v>549164</v>
       </c>
       <c r="R11" t="n">
-        <v>7198165</v>
+        <v>7198193</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497183</v>
+        <v>121497172</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549164</v>
+        <v>549180</v>
       </c>
       <c r="R12" t="n">
-        <v>7198193</v>
+        <v>7198099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497180</v>
+        <v>121497165</v>
       </c>
       <c r="B13" t="n">
-        <v>57508</v>
+        <v>79691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,38 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549163</v>
+        <v>549099</v>
       </c>
       <c r="R13" t="n">
-        <v>7198196</v>
+        <v>7197953</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497182</v>
+        <v>121497164</v>
       </c>
       <c r="B14" t="n">
-        <v>82392</v>
+        <v>79719</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549164</v>
+        <v>549099</v>
       </c>
       <c r="R14" t="n">
-        <v>7198194</v>
+        <v>7197953</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497204</v>
+        <v>121497201</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>91006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548901</v>
+        <v>548884</v>
       </c>
       <c r="R15" t="n">
-        <v>7198259</v>
+        <v>7198317</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497201</v>
+        <v>121497190</v>
       </c>
       <c r="B16" t="n">
-        <v>91005</v>
+        <v>79691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548884</v>
+        <v>549134</v>
       </c>
       <c r="R16" t="n">
-        <v>7198317</v>
+        <v>7198295</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497208</v>
+        <v>121497161</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548950</v>
+        <v>549102</v>
       </c>
       <c r="R17" t="n">
-        <v>7198094</v>
+        <v>7197710</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497200</v>
+        <v>121497170</v>
       </c>
       <c r="B18" t="n">
-        <v>91159</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,25 +2489,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548885</v>
+        <v>549175</v>
       </c>
       <c r="R18" t="n">
-        <v>7198318</v>
+        <v>7198087</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2561,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497192</v>
+        <v>121497163</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>97059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2601,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2638,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549086</v>
+        <v>549066</v>
       </c>
       <c r="R19" t="n">
-        <v>7198360</v>
+        <v>7197912</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497179</v>
+        <v>121497195</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549168</v>
+        <v>548975</v>
       </c>
       <c r="R20" t="n">
-        <v>7198189</v>
+        <v>7198330</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2785,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497163</v>
+        <v>121497177</v>
       </c>
       <c r="B21" t="n">
-        <v>97058</v>
+        <v>79691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2825,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549066</v>
+        <v>549194</v>
       </c>
       <c r="R21" t="n">
-        <v>7197912</v>
+        <v>7198164</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2907,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497166</v>
+        <v>121497192</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549115</v>
+        <v>549086</v>
       </c>
       <c r="R22" t="n">
-        <v>7197960</v>
+        <v>7198360</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3019,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497181</v>
+        <v>121497179</v>
       </c>
       <c r="B23" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,39 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549164</v>
+        <v>549168</v>
       </c>
       <c r="R23" t="n">
-        <v>7198195</v>
+        <v>7198189</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497173</v>
+        <v>121497202</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,25 +3161,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549182</v>
+        <v>548884</v>
       </c>
       <c r="R24" t="n">
-        <v>7198123</v>
+        <v>7198316</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3238,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497190</v>
+        <v>121497178</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>79719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3315,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549134</v>
+        <v>549168</v>
       </c>
       <c r="R25" t="n">
-        <v>7198295</v>
+        <v>7198189</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3350,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497209</v>
+        <v>121497168</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>79691</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3403,39 +3389,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549014</v>
+        <v>549146</v>
       </c>
       <c r="R26" t="n">
-        <v>7198006</v>
+        <v>7198067</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3467,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3477,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497205</v>
+        <v>121497208</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3549,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548901</v>
+        <v>548950</v>
       </c>
       <c r="R27" t="n">
-        <v>7198259</v>
+        <v>7198094</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3584,7 +3565,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3594,7 +3575,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497161</v>
+        <v>121497191</v>
       </c>
       <c r="B28" t="n">
-        <v>57355</v>
+        <v>74699</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,43 +3614,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549102</v>
+        <v>549086</v>
       </c>
       <c r="R28" t="n">
-        <v>7197710</v>
+        <v>7198360</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3701,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497193</v>
+        <v>121497182</v>
       </c>
       <c r="B29" t="n">
-        <v>57355</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,39 +3730,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549039</v>
+        <v>549164</v>
       </c>
       <c r="R29" t="n">
-        <v>7198351</v>
+        <v>7198194</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3818,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3828,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497184</v>
+        <v>121497167</v>
       </c>
       <c r="B30" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3871,21 +3842,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3895,10 +3866,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549161</v>
+        <v>549130</v>
       </c>
       <c r="R30" t="n">
-        <v>7198220</v>
+        <v>7198017</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3930,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3940,7 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,10 +3938,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497206</v>
+        <v>121497180</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3983,34 +3954,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548952</v>
+        <v>549163</v>
       </c>
       <c r="R31" t="n">
-        <v>7198228</v>
+        <v>7198196</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4042,7 +4017,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4052,7 +4027,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,10 +4054,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497191</v>
+        <v>121497185</v>
       </c>
       <c r="B32" t="n">
-        <v>74698</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4091,25 +4066,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549086</v>
+        <v>549161</v>
       </c>
       <c r="R32" t="n">
-        <v>7198360</v>
+        <v>7198217</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4154,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4164,7 +4139,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4191,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497168</v>
+        <v>121497181</v>
       </c>
       <c r="B33" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4207,34 +4182,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549146</v>
+        <v>549164</v>
       </c>
       <c r="R33" t="n">
-        <v>7198067</v>
+        <v>7198195</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4266,7 +4246,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4276,7 +4256,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,10 +4283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497202</v>
+        <v>121497189</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4319,21 +4299,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4343,10 +4323,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548884</v>
+        <v>549139</v>
       </c>
       <c r="R34" t="n">
-        <v>7198316</v>
+        <v>7198261</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4358,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4368,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4395,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497170</v>
+        <v>121497205</v>
       </c>
       <c r="B35" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4431,34 +4411,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549175</v>
+        <v>548901</v>
       </c>
       <c r="R35" t="n">
-        <v>7198087</v>
+        <v>7198259</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4475,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4485,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4512,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497186</v>
+        <v>121497184</v>
       </c>
       <c r="B36" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,10 +4552,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549143</v>
+        <v>549161</v>
       </c>
       <c r="R36" t="n">
-        <v>7198250</v>
+        <v>7198220</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4587,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4597,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,10 +4624,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497189</v>
+        <v>121497186</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,10 +4664,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549139</v>
+        <v>549143</v>
       </c>
       <c r="R37" t="n">
-        <v>7198261</v>
+        <v>7198250</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4714,7 +4699,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4724,7 +4709,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,10 +4736,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497169</v>
+        <v>121497207</v>
       </c>
       <c r="B38" t="n">
-        <v>79718</v>
+        <v>57356</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,38 +4748,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549145</v>
+        <v>548954</v>
       </c>
       <c r="R38" t="n">
-        <v>7198071</v>
+        <v>7198216</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4826,7 +4816,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4836,7 +4826,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,10 +4853,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497188</v>
+        <v>121497187</v>
       </c>
       <c r="B39" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,21 +4869,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4906,7 +4896,7 @@
         <v>549143</v>
       </c>
       <c r="R39" t="n">
-        <v>7198251</v>
+        <v>7198250</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4938,7 +4928,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,7 +4938,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,10 +4965,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497174</v>
+        <v>121497193</v>
       </c>
       <c r="B40" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4991,34 +4981,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549183</v>
+        <v>549039</v>
       </c>
       <c r="R40" t="n">
-        <v>7198122</v>
+        <v>7198351</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5050,7 +5045,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,7 +5055,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5090,7 +5085,7 @@
         <v>121497171</v>
       </c>
       <c r="B41" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5204,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497165</v>
+        <v>121497194</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,21 +5215,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549099</v>
+        <v>549039</v>
       </c>
       <c r="R42" t="n">
-        <v>7197953</v>
+        <v>7198351</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,10 +5311,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497194</v>
+        <v>121497209</v>
       </c>
       <c r="B43" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,34 +5327,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549039</v>
+        <v>549014</v>
       </c>
       <c r="R43" t="n">
-        <v>7198351</v>
+        <v>7198006</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497207</v>
+        <v>121497166</v>
       </c>
       <c r="B44" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5444,39 +5444,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548954</v>
+        <v>549115</v>
       </c>
       <c r="R44" t="n">
-        <v>7198216</v>
+        <v>7197960</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497195</v>
+        <v>121497162</v>
       </c>
       <c r="B45" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5561,34 +5556,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548975</v>
+        <v>549089</v>
       </c>
       <c r="R45" t="n">
-        <v>7198330</v>
+        <v>7197751</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497164</v>
+        <v>121497174</v>
       </c>
       <c r="B46" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5669,25 +5669,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549099</v>
+        <v>549183</v>
       </c>
       <c r="R46" t="n">
-        <v>7197953</v>
+        <v>7198122</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497173</v>
+        <v>121497180</v>
       </c>
       <c r="B2" t="n">
-        <v>79719</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549182</v>
+        <v>549163</v>
       </c>
       <c r="R2" t="n">
-        <v>7198123</v>
+        <v>7198196</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497176</v>
+        <v>121497169</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549145</v>
       </c>
       <c r="R3" t="n">
-        <v>7198165</v>
+        <v>7198071</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497169</v>
+        <v>121497202</v>
       </c>
       <c r="B4" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549145</v>
+        <v>548884</v>
       </c>
       <c r="R4" t="n">
-        <v>7198071</v>
+        <v>7198316</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497203</v>
+        <v>121497186</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548894</v>
+        <v>549143</v>
       </c>
       <c r="R5" t="n">
-        <v>7198284</v>
+        <v>7198250</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497204</v>
+        <v>121497189</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548901</v>
+        <v>549139</v>
       </c>
       <c r="R6" t="n">
-        <v>7198259</v>
+        <v>7198261</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497200</v>
+        <v>121497193</v>
       </c>
       <c r="B7" t="n">
-        <v>91160</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,38 +1251,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548885</v>
+        <v>549039</v>
       </c>
       <c r="R7" t="n">
-        <v>7198318</v>
+        <v>7198351</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497175</v>
+        <v>121497205</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1372,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549197</v>
+        <v>548901</v>
       </c>
       <c r="R8" t="n">
-        <v>7198165</v>
+        <v>7198259</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497206</v>
+        <v>121497176</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1499,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548952</v>
+        <v>549196</v>
       </c>
       <c r="R9" t="n">
-        <v>7198228</v>
+        <v>7198165</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497188</v>
+        <v>121497168</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549143</v>
+        <v>549146</v>
       </c>
       <c r="R10" t="n">
-        <v>7198251</v>
+        <v>7198067</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497183</v>
+        <v>121497194</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1723,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549164</v>
+        <v>549039</v>
       </c>
       <c r="R11" t="n">
-        <v>7198193</v>
+        <v>7198351</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497172</v>
+        <v>121497187</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,39 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549180</v>
+        <v>549143</v>
       </c>
       <c r="R12" t="n">
-        <v>7198099</v>
+        <v>7198250</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497165</v>
+        <v>121497161</v>
       </c>
       <c r="B13" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1937,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549099</v>
+        <v>549102</v>
       </c>
       <c r="R13" t="n">
-        <v>7197953</v>
+        <v>7197710</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497164</v>
+        <v>121497174</v>
       </c>
       <c r="B14" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2050,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549099</v>
+        <v>549183</v>
       </c>
       <c r="R14" t="n">
-        <v>7197953</v>
+        <v>7198122</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497201</v>
+        <v>121497184</v>
       </c>
       <c r="B15" t="n">
-        <v>91006</v>
+        <v>79691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2166,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548884</v>
+        <v>549161</v>
       </c>
       <c r="R15" t="n">
-        <v>7198317</v>
+        <v>7198220</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497190</v>
+        <v>121497206</v>
       </c>
       <c r="B16" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2278,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549134</v>
+        <v>548952</v>
       </c>
       <c r="R16" t="n">
-        <v>7198295</v>
+        <v>7198228</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2347,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497161</v>
+        <v>121497204</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,39 +2390,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549102</v>
+        <v>548901</v>
       </c>
       <c r="R17" t="n">
-        <v>7197710</v>
+        <v>7198259</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2449,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2459,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497170</v>
+        <v>121497201</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,21 +2502,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549175</v>
+        <v>548884</v>
       </c>
       <c r="R18" t="n">
-        <v>7198087</v>
+        <v>7198317</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2571,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497163</v>
+        <v>121497203</v>
       </c>
       <c r="B19" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,25 +2610,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549066</v>
+        <v>548894</v>
       </c>
       <c r="R19" t="n">
-        <v>7197912</v>
+        <v>7198284</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2673,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2683,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497195</v>
+        <v>121497181</v>
       </c>
       <c r="B20" t="n">
-        <v>79691</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,34 +2726,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548975</v>
+        <v>549164</v>
       </c>
       <c r="R20" t="n">
-        <v>7198330</v>
+        <v>7198195</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2827,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497177</v>
+        <v>121497190</v>
       </c>
       <c r="B21" t="n">
         <v>79691</v>
@@ -2853,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549194</v>
+        <v>549134</v>
       </c>
       <c r="R21" t="n">
-        <v>7198164</v>
+        <v>7198295</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497192</v>
+        <v>121497195</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2955,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2979,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549086</v>
+        <v>548975</v>
       </c>
       <c r="R22" t="n">
-        <v>7198360</v>
+        <v>7198330</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3014,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3024,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497179</v>
+        <v>121497163</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3063,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3091,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549168</v>
+        <v>549066</v>
       </c>
       <c r="R23" t="n">
-        <v>7198189</v>
+        <v>7197912</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3126,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3136,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497202</v>
+        <v>121497177</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3179,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548884</v>
+        <v>549194</v>
       </c>
       <c r="R24" t="n">
-        <v>7198316</v>
+        <v>7198164</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497178</v>
+        <v>121497162</v>
       </c>
       <c r="B25" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,38 +3287,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549168</v>
+        <v>549089</v>
       </c>
       <c r="R25" t="n">
-        <v>7198189</v>
+        <v>7197751</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497168</v>
+        <v>121497209</v>
       </c>
       <c r="B26" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,34 +3408,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549146</v>
+        <v>549014</v>
       </c>
       <c r="R26" t="n">
-        <v>7198067</v>
+        <v>7198006</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3472,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3482,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497208</v>
+        <v>121497167</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,39 +3525,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548950</v>
+        <v>549130</v>
       </c>
       <c r="R27" t="n">
-        <v>7198094</v>
+        <v>7198017</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3565,7 +3584,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3594,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,10 +3621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497191</v>
+        <v>121497200</v>
       </c>
       <c r="B28" t="n">
-        <v>74699</v>
+        <v>91160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,25 +3633,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3642,10 +3661,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549086</v>
+        <v>548885</v>
       </c>
       <c r="R28" t="n">
-        <v>7198360</v>
+        <v>7198318</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3677,7 +3696,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3706,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,7 +3845,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497167</v>
+        <v>121497179</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3866,10 +3885,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549130</v>
+        <v>549168</v>
       </c>
       <c r="R30" t="n">
-        <v>7198017</v>
+        <v>7198189</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3901,7 +3920,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3930,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497180</v>
+        <v>121497207</v>
       </c>
       <c r="B31" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3954,26 +3973,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3982,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549163</v>
+        <v>548954</v>
       </c>
       <c r="R31" t="n">
-        <v>7198196</v>
+        <v>7198216</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4017,7 +4037,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4027,7 +4047,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4054,10 +4074,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497185</v>
+        <v>121497175</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,21 +4090,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4094,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549161</v>
+        <v>549197</v>
       </c>
       <c r="R32" t="n">
-        <v>7198217</v>
+        <v>7198165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4129,7 +4149,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,7 +4159,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4166,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497181</v>
+        <v>121497183</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4182,29 +4202,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
@@ -4214,7 +4229,7 @@
         <v>549164</v>
       </c>
       <c r="R33" t="n">
-        <v>7198195</v>
+        <v>7198193</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4283,10 +4298,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497189</v>
+        <v>121497172</v>
       </c>
       <c r="B34" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4299,34 +4314,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549139</v>
+        <v>549180</v>
       </c>
       <c r="R34" t="n">
-        <v>7198261</v>
+        <v>7198099</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4358,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4368,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4395,10 +4415,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497205</v>
+        <v>121497170</v>
       </c>
       <c r="B35" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4411,39 +4431,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548901</v>
+        <v>549175</v>
       </c>
       <c r="R35" t="n">
-        <v>7198259</v>
+        <v>7198087</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4475,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4485,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497184</v>
+        <v>121497164</v>
       </c>
       <c r="B36" t="n">
-        <v>79691</v>
+        <v>79719</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4524,25 +4539,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4552,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549161</v>
+        <v>549099</v>
       </c>
       <c r="R36" t="n">
-        <v>7198220</v>
+        <v>7197953</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4587,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4597,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497186</v>
+        <v>121497191</v>
       </c>
       <c r="B37" t="n">
-        <v>79691</v>
+        <v>74699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4636,25 +4651,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4664,10 +4679,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549143</v>
+        <v>549086</v>
       </c>
       <c r="R37" t="n">
-        <v>7198250</v>
+        <v>7198360</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4699,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4709,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497207</v>
+        <v>121497192</v>
       </c>
       <c r="B38" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4752,39 +4767,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548954</v>
+        <v>549086</v>
       </c>
       <c r="R38" t="n">
-        <v>7198216</v>
+        <v>7198360</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4816,7 +4826,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4826,7 +4836,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497187</v>
+        <v>121497185</v>
       </c>
       <c r="B39" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4869,21 +4879,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4893,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549143</v>
+        <v>549161</v>
       </c>
       <c r="R39" t="n">
-        <v>7198250</v>
+        <v>7198217</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4928,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4938,7 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4965,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497193</v>
+        <v>121497173</v>
       </c>
       <c r="B40" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4977,43 +4987,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549039</v>
+        <v>549182</v>
       </c>
       <c r="R40" t="n">
-        <v>7198351</v>
+        <v>7198123</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5045,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5055,7 +5060,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5082,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497171</v>
+        <v>121497178</v>
       </c>
       <c r="B41" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5094,43 +5099,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549185</v>
+        <v>549168</v>
       </c>
       <c r="R41" t="n">
-        <v>7198089</v>
+        <v>7198189</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,7 +5199,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497194</v>
+        <v>121497188</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549039</v>
+        <v>549143</v>
       </c>
       <c r="R42" t="n">
-        <v>7198351</v>
+        <v>7198251</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497209</v>
+        <v>121497208</v>
       </c>
       <c r="B43" t="n">
         <v>57356</v>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549014</v>
+        <v>548950</v>
       </c>
       <c r="R43" t="n">
-        <v>7198006</v>
+        <v>7198094</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497166</v>
+        <v>121497165</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549115</v>
+        <v>549099</v>
       </c>
       <c r="R44" t="n">
-        <v>7197960</v>
+        <v>7197953</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497162</v>
+        <v>121497166</v>
       </c>
       <c r="B45" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5556,39 +5556,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549089</v>
+        <v>549115</v>
       </c>
       <c r="R45" t="n">
-        <v>7197751</v>
+        <v>7197960</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5615,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5625,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497174</v>
+        <v>121497171</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,34 +5668,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549183</v>
+        <v>549185</v>
       </c>
       <c r="R46" t="n">
-        <v>7198122</v>
+        <v>7198089</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497180</v>
+        <v>121497208</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549163</v>
+        <v>548950</v>
       </c>
       <c r="R2" t="n">
-        <v>7198196</v>
+        <v>7198094</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497169</v>
+        <v>121497202</v>
       </c>
       <c r="B3" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549145</v>
+        <v>548884</v>
       </c>
       <c r="R3" t="n">
-        <v>7198071</v>
+        <v>7198316</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497202</v>
+        <v>121497207</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548884</v>
+        <v>548954</v>
       </c>
       <c r="R4" t="n">
-        <v>7198316</v>
+        <v>7198216</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497186</v>
+        <v>121497205</v>
       </c>
       <c r="B5" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549143</v>
+        <v>548901</v>
       </c>
       <c r="R5" t="n">
-        <v>7198250</v>
+        <v>7198259</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497189</v>
+        <v>121497172</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549139</v>
+        <v>549180</v>
       </c>
       <c r="R6" t="n">
-        <v>7198261</v>
+        <v>7198099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497193</v>
+        <v>121497171</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1275,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549039</v>
+        <v>549185</v>
       </c>
       <c r="R7" t="n">
-        <v>7198351</v>
+        <v>7198089</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497205</v>
+        <v>121497194</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548901</v>
+        <v>549039</v>
       </c>
       <c r="R8" t="n">
-        <v>7198259</v>
+        <v>7198351</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497176</v>
+        <v>121497164</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549196</v>
+        <v>549099</v>
       </c>
       <c r="R9" t="n">
-        <v>7198165</v>
+        <v>7197953</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497168</v>
+        <v>121497187</v>
       </c>
       <c r="B10" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,21 +1612,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549146</v>
+        <v>549143</v>
       </c>
       <c r="R10" t="n">
-        <v>7198067</v>
+        <v>7198250</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497194</v>
+        <v>121497161</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,34 +1724,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549039</v>
+        <v>549102</v>
       </c>
       <c r="R11" t="n">
-        <v>7198351</v>
+        <v>7197710</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497187</v>
+        <v>121497174</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549143</v>
+        <v>549183</v>
       </c>
       <c r="R12" t="n">
-        <v>7198250</v>
+        <v>7198122</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497161</v>
+        <v>121497188</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,39 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549102</v>
+        <v>549143</v>
       </c>
       <c r="R13" t="n">
-        <v>7197710</v>
+        <v>7198251</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497174</v>
+        <v>121497191</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549183</v>
+        <v>549086</v>
       </c>
       <c r="R14" t="n">
-        <v>7198122</v>
+        <v>7198360</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497184</v>
+        <v>121497173</v>
       </c>
       <c r="B15" t="n">
-        <v>79691</v>
+        <v>79719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,25 +2173,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549161</v>
+        <v>549182</v>
       </c>
       <c r="R15" t="n">
-        <v>7198220</v>
+        <v>7198123</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497206</v>
+        <v>121497167</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2302,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548952</v>
+        <v>549130</v>
       </c>
       <c r="R16" t="n">
-        <v>7198228</v>
+        <v>7198017</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497201</v>
+        <v>121497190</v>
       </c>
       <c r="B18" t="n">
-        <v>91006</v>
+        <v>79691</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,21 +2513,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548884</v>
+        <v>549134</v>
       </c>
       <c r="R18" t="n">
-        <v>7198317</v>
+        <v>7198295</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2561,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497203</v>
+        <v>121497162</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,34 +2625,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548894</v>
+        <v>549089</v>
       </c>
       <c r="R19" t="n">
-        <v>7198284</v>
+        <v>7197751</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497181</v>
+        <v>121497193</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,16 +2742,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2755,10 +2771,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549164</v>
+        <v>549039</v>
       </c>
       <c r="R20" t="n">
-        <v>7198195</v>
+        <v>7198351</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2806,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2816,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,7 +2843,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497190</v>
+        <v>121497186</v>
       </c>
       <c r="B21" t="n">
         <v>79691</v>
@@ -2867,10 +2883,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549134</v>
+        <v>549143</v>
       </c>
       <c r="R21" t="n">
-        <v>7198295</v>
+        <v>7198250</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497195</v>
+        <v>121497183</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,21 +2971,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2979,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548975</v>
+        <v>549164</v>
       </c>
       <c r="R22" t="n">
-        <v>7198330</v>
+        <v>7198193</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +3030,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3040,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,10 +3067,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497163</v>
+        <v>121497170</v>
       </c>
       <c r="B23" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,25 +3079,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3091,10 +3107,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549066</v>
+        <v>549175</v>
       </c>
       <c r="R23" t="n">
-        <v>7197912</v>
+        <v>7198087</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +3142,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3152,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497177</v>
+        <v>121497181</v>
       </c>
       <c r="B24" t="n">
-        <v>79691</v>
+        <v>57372</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,34 +3195,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549194</v>
+        <v>549164</v>
       </c>
       <c r="R24" t="n">
-        <v>7198164</v>
+        <v>7198195</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3238,7 +3259,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3269,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,10 +3296,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497162</v>
+        <v>121497200</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,43 +3308,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549089</v>
+        <v>548885</v>
       </c>
       <c r="R25" t="n">
-        <v>7197751</v>
+        <v>7198318</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3355,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3381,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3408,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497209</v>
+        <v>121497166</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,39 +3424,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549014</v>
+        <v>549115</v>
       </c>
       <c r="R26" t="n">
-        <v>7198006</v>
+        <v>7197960</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3472,7 +3483,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3482,7 +3493,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3520,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497167</v>
+        <v>121497178</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,25 +3532,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3549,10 +3560,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549130</v>
+        <v>549168</v>
       </c>
       <c r="R27" t="n">
-        <v>7198017</v>
+        <v>7198189</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3584,7 +3595,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3594,7 +3605,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,10 +3632,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497200</v>
+        <v>121497201</v>
       </c>
       <c r="B28" t="n">
-        <v>91160</v>
+        <v>91006</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,25 +3644,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3661,10 +3672,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548885</v>
+        <v>548884</v>
       </c>
       <c r="R28" t="n">
-        <v>7198318</v>
+        <v>7198317</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3733,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497182</v>
+        <v>121497180</v>
       </c>
       <c r="B29" t="n">
-        <v>82393</v>
+        <v>57509</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3749,34 +3760,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549164</v>
+        <v>549163</v>
       </c>
       <c r="R29" t="n">
-        <v>7198194</v>
+        <v>7198196</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3845,10 +3860,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497179</v>
+        <v>121497209</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3861,34 +3876,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549168</v>
+        <v>549014</v>
       </c>
       <c r="R30" t="n">
-        <v>7198189</v>
+        <v>7198006</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3920,7 +3940,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3930,7 +3950,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3957,10 +3977,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497207</v>
+        <v>121497165</v>
       </c>
       <c r="B31" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,39 +3993,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548954</v>
+        <v>549099</v>
       </c>
       <c r="R31" t="n">
-        <v>7198216</v>
+        <v>7197953</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4037,7 +4052,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4047,7 +4062,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,10 +4089,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497175</v>
+        <v>121497163</v>
       </c>
       <c r="B32" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,25 +4101,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4129,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549197</v>
+        <v>549066</v>
       </c>
       <c r="R32" t="n">
-        <v>7198165</v>
+        <v>7197912</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4149,7 +4164,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4174,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,7 +4201,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497183</v>
+        <v>121497179</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549164</v>
+        <v>549168</v>
       </c>
       <c r="R33" t="n">
-        <v>7198193</v>
+        <v>7198189</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4261,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4271,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,10 +4313,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497172</v>
+        <v>121497169</v>
       </c>
       <c r="B34" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,43 +4325,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549180</v>
+        <v>549145</v>
       </c>
       <c r="R34" t="n">
-        <v>7198099</v>
+        <v>7198071</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4388,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4398,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4425,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497170</v>
+        <v>121497195</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4431,21 +4441,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4455,10 +4465,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549175</v>
+        <v>548975</v>
       </c>
       <c r="R35" t="n">
-        <v>7198087</v>
+        <v>7198330</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4500,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4510,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497164</v>
+        <v>121497182</v>
       </c>
       <c r="B36" t="n">
-        <v>79719</v>
+        <v>82393</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,25 +4549,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4567,10 +4577,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549099</v>
+        <v>549164</v>
       </c>
       <c r="R36" t="n">
-        <v>7197953</v>
+        <v>7198194</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497191</v>
+        <v>121497175</v>
       </c>
       <c r="B37" t="n">
-        <v>74699</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,25 +4661,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4679,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549086</v>
+        <v>549197</v>
       </c>
       <c r="R37" t="n">
-        <v>7198360</v>
+        <v>7198165</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4714,7 +4724,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4724,7 +4734,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,7 +4761,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497192</v>
+        <v>121497185</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4791,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549086</v>
+        <v>549161</v>
       </c>
       <c r="R38" t="n">
-        <v>7198360</v>
+        <v>7198217</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4826,7 +4836,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4836,7 +4846,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,7 +4873,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497185</v>
+        <v>121497176</v>
       </c>
       <c r="B39" t="n">
         <v>78609</v>
@@ -4903,10 +4913,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549161</v>
+        <v>549196</v>
       </c>
       <c r="R39" t="n">
-        <v>7198217</v>
+        <v>7198165</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4938,7 +4948,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,7 +4958,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,10 +4985,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497173</v>
+        <v>121497177</v>
       </c>
       <c r="B40" t="n">
-        <v>79719</v>
+        <v>79691</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4987,25 +4997,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5015,10 +5025,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549182</v>
+        <v>549194</v>
       </c>
       <c r="R40" t="n">
-        <v>7198123</v>
+        <v>7198164</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5050,7 +5060,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,7 +5070,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,10 +5097,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497178</v>
+        <v>121497184</v>
       </c>
       <c r="B41" t="n">
-        <v>79719</v>
+        <v>79691</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5099,25 +5109,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549168</v>
+        <v>549161</v>
       </c>
       <c r="R41" t="n">
-        <v>7198189</v>
+        <v>7198220</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5162,7 +5172,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,7 +5182,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5209,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497188</v>
+        <v>121497168</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5215,21 +5225,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5239,10 +5249,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549143</v>
+        <v>549146</v>
       </c>
       <c r="R42" t="n">
-        <v>7198251</v>
+        <v>7198067</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5274,7 +5284,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,7 +5294,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5311,10 +5321,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497208</v>
+        <v>121497192</v>
       </c>
       <c r="B43" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,39 +5337,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548950</v>
+        <v>549086</v>
       </c>
       <c r="R43" t="n">
-        <v>7198094</v>
+        <v>7198360</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5396,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5406,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,7 +5433,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497165</v>
+        <v>121497189</v>
       </c>
       <c r="B44" t="n">
         <v>79691</v>
@@ -5468,10 +5473,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549099</v>
+        <v>549139</v>
       </c>
       <c r="R44" t="n">
-        <v>7197953</v>
+        <v>7198261</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5508,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5518,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,7 +5545,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497166</v>
+        <v>121497203</v>
       </c>
       <c r="B45" t="n">
         <v>78609</v>
@@ -5580,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549115</v>
+        <v>548894</v>
       </c>
       <c r="R45" t="n">
-        <v>7197960</v>
+        <v>7198284</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5615,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5625,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497171</v>
+        <v>121497206</v>
       </c>
       <c r="B46" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5668,39 +5673,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549185</v>
+        <v>548952</v>
       </c>
       <c r="R46" t="n">
-        <v>7198089</v>
+        <v>7198228</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497208</v>
+        <v>121497192</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548950</v>
+        <v>549086</v>
       </c>
       <c r="R2" t="n">
-        <v>7198094</v>
+        <v>7198360</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497202</v>
+        <v>121497194</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548884</v>
+        <v>549039</v>
       </c>
       <c r="R3" t="n">
-        <v>7198316</v>
+        <v>7198351</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497207</v>
+        <v>121497175</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548954</v>
+        <v>549197</v>
       </c>
       <c r="R4" t="n">
-        <v>7198216</v>
+        <v>7198165</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497205</v>
+        <v>121497182</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548901</v>
+        <v>549164</v>
       </c>
       <c r="R5" t="n">
-        <v>7198259</v>
+        <v>7198194</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497172</v>
+        <v>121497188</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549180</v>
+        <v>549143</v>
       </c>
       <c r="R6" t="n">
-        <v>7198099</v>
+        <v>7198251</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497171</v>
+        <v>121497169</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,43 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549185</v>
+        <v>549145</v>
       </c>
       <c r="R7" t="n">
-        <v>7198089</v>
+        <v>7198071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497194</v>
+        <v>121497162</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549039</v>
+        <v>549089</v>
       </c>
       <c r="R8" t="n">
-        <v>7198351</v>
+        <v>7197751</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497164</v>
+        <v>121497173</v>
       </c>
       <c r="B9" t="n">
         <v>79719</v>
@@ -1524,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549099</v>
+        <v>549182</v>
       </c>
       <c r="R9" t="n">
-        <v>7197953</v>
+        <v>7198123</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497187</v>
+        <v>121497189</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549143</v>
+        <v>549139</v>
       </c>
       <c r="R10" t="n">
-        <v>7198250</v>
+        <v>7198261</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497161</v>
+        <v>121497181</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,16 +1704,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1744,7 +1724,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1753,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549102</v>
+        <v>549164</v>
       </c>
       <c r="R11" t="n">
-        <v>7197710</v>
+        <v>7198195</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497174</v>
+        <v>121497161</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549183</v>
+        <v>549102</v>
       </c>
       <c r="R12" t="n">
-        <v>7198122</v>
+        <v>7197710</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497188</v>
+        <v>121497163</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549143</v>
+        <v>549066</v>
       </c>
       <c r="R13" t="n">
-        <v>7198251</v>
+        <v>7197912</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497191</v>
+        <v>121497186</v>
       </c>
       <c r="B14" t="n">
-        <v>74699</v>
+        <v>79691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549086</v>
+        <v>549143</v>
       </c>
       <c r="R14" t="n">
-        <v>7198360</v>
+        <v>7198250</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497173</v>
+        <v>121497204</v>
       </c>
       <c r="B15" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549182</v>
+        <v>548901</v>
       </c>
       <c r="R15" t="n">
-        <v>7198123</v>
+        <v>7198259</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497167</v>
+        <v>121497191</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,25 +2270,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549130</v>
+        <v>549086</v>
       </c>
       <c r="R16" t="n">
-        <v>7198017</v>
+        <v>7198360</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497204</v>
+        <v>121497205</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,24 +2386,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
@@ -2497,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497190</v>
+        <v>121497193</v>
       </c>
       <c r="B18" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,34 +2503,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549134</v>
+        <v>549039</v>
       </c>
       <c r="R18" t="n">
-        <v>7198295</v>
+        <v>7198351</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497162</v>
+        <v>121497187</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,39 +2620,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549089</v>
+        <v>549143</v>
       </c>
       <c r="R19" t="n">
-        <v>7197751</v>
+        <v>7198250</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497193</v>
+        <v>121497177</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,39 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549039</v>
+        <v>549194</v>
       </c>
       <c r="R20" t="n">
-        <v>7198351</v>
+        <v>7198164</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2806,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2816,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497186</v>
+        <v>121497172</v>
       </c>
       <c r="B21" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,34 +2844,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549143</v>
+        <v>549180</v>
       </c>
       <c r="R21" t="n">
-        <v>7198250</v>
+        <v>7198099</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2918,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497183</v>
+        <v>121497184</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,21 +2961,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549164</v>
+        <v>549161</v>
       </c>
       <c r="R22" t="n">
-        <v>7198193</v>
+        <v>7198220</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3030,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497170</v>
+        <v>121497185</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3083,21 +3073,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3107,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549175</v>
+        <v>549161</v>
       </c>
       <c r="R23" t="n">
-        <v>7198087</v>
+        <v>7198217</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3142,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3152,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497181</v>
+        <v>121497179</v>
       </c>
       <c r="B24" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,39 +3185,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549164</v>
+        <v>549168</v>
       </c>
       <c r="R24" t="n">
-        <v>7198195</v>
+        <v>7198189</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3259,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3269,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497200</v>
+        <v>121497166</v>
       </c>
       <c r="B25" t="n">
-        <v>91160</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,25 +3293,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3336,10 +3321,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548885</v>
+        <v>549115</v>
       </c>
       <c r="R25" t="n">
-        <v>7198318</v>
+        <v>7197960</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3371,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497166</v>
+        <v>121497206</v>
       </c>
       <c r="B26" t="n">
         <v>78609</v>
@@ -3448,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549115</v>
+        <v>548952</v>
       </c>
       <c r="R26" t="n">
-        <v>7197960</v>
+        <v>7198228</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3483,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3493,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497178</v>
+        <v>121497203</v>
       </c>
       <c r="B27" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3532,25 +3517,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3560,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549168</v>
+        <v>548894</v>
       </c>
       <c r="R27" t="n">
-        <v>7198189</v>
+        <v>7198284</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3595,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3605,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497201</v>
+        <v>121497207</v>
       </c>
       <c r="B28" t="n">
-        <v>91006</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3648,34 +3633,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548884</v>
+        <v>548954</v>
       </c>
       <c r="R28" t="n">
-        <v>7198317</v>
+        <v>7198216</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3707,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3717,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497180</v>
+        <v>121497202</v>
       </c>
       <c r="B29" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,38 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549163</v>
+        <v>548884</v>
       </c>
       <c r="R29" t="n">
-        <v>7198196</v>
+        <v>7198316</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3823,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3833,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497209</v>
+        <v>121497200</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,43 +3858,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549014</v>
+        <v>548885</v>
       </c>
       <c r="R30" t="n">
-        <v>7198006</v>
+        <v>7198318</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3940,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3950,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,7 +3958,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497165</v>
+        <v>121497190</v>
       </c>
       <c r="B31" t="n">
         <v>79691</v>
@@ -4017,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549099</v>
+        <v>549134</v>
       </c>
       <c r="R31" t="n">
-        <v>7197953</v>
+        <v>7198295</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4052,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4062,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497163</v>
+        <v>121497201</v>
       </c>
       <c r="B32" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4101,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4129,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549066</v>
+        <v>548884</v>
       </c>
       <c r="R32" t="n">
-        <v>7197912</v>
+        <v>7198317</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4164,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4174,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4201,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497179</v>
+        <v>121497171</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4217,34 +4198,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549168</v>
+        <v>549185</v>
       </c>
       <c r="R33" t="n">
-        <v>7198189</v>
+        <v>7198089</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4276,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497169</v>
+        <v>121497165</v>
       </c>
       <c r="B34" t="n">
-        <v>79719</v>
+        <v>79691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4325,25 +4311,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4353,10 +4339,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549145</v>
+        <v>549099</v>
       </c>
       <c r="R34" t="n">
-        <v>7198071</v>
+        <v>7197953</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4388,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4398,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4425,7 +4411,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497195</v>
+        <v>121497168</v>
       </c>
       <c r="B35" t="n">
         <v>79691</v>
@@ -4465,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548975</v>
+        <v>549146</v>
       </c>
       <c r="R35" t="n">
-        <v>7198330</v>
+        <v>7198067</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4500,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4510,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497182</v>
+        <v>121497180</v>
       </c>
       <c r="B36" t="n">
-        <v>82393</v>
+        <v>57509</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4553,34 +4539,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549164</v>
+        <v>549163</v>
       </c>
       <c r="R36" t="n">
-        <v>7198194</v>
+        <v>7198196</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4649,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497175</v>
+        <v>121497195</v>
       </c>
       <c r="B37" t="n">
-        <v>90738</v>
+        <v>79691</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4665,21 +4655,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4689,10 +4679,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549197</v>
+        <v>548975</v>
       </c>
       <c r="R37" t="n">
-        <v>7198165</v>
+        <v>7198330</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4724,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4734,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,7 +4751,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497185</v>
+        <v>121497174</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4801,10 +4791,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549161</v>
+        <v>549183</v>
       </c>
       <c r="R38" t="n">
-        <v>7198217</v>
+        <v>7198122</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4836,7 +4826,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4846,7 +4836,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4873,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497176</v>
+        <v>121497170</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,21 +4879,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4913,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549196</v>
+        <v>549175</v>
       </c>
       <c r="R39" t="n">
-        <v>7198165</v>
+        <v>7198087</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4948,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4958,7 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4985,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497177</v>
+        <v>121497164</v>
       </c>
       <c r="B40" t="n">
-        <v>79691</v>
+        <v>79719</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4997,25 +4987,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5025,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549194</v>
+        <v>549099</v>
       </c>
       <c r="R40" t="n">
-        <v>7198164</v>
+        <v>7197953</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5060,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5070,7 +5060,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497184</v>
+        <v>121497183</v>
       </c>
       <c r="B41" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5113,21 +5103,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5137,10 +5127,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549161</v>
+        <v>549164</v>
       </c>
       <c r="R41" t="n">
-        <v>7198220</v>
+        <v>7198193</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5172,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5182,7 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497168</v>
+        <v>121497176</v>
       </c>
       <c r="B42" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5225,21 +5215,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5249,10 +5239,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549146</v>
+        <v>549196</v>
       </c>
       <c r="R42" t="n">
-        <v>7198067</v>
+        <v>7198165</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5284,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5294,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5321,7 +5311,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497192</v>
+        <v>121497167</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5361,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549086</v>
+        <v>549130</v>
       </c>
       <c r="R43" t="n">
-        <v>7198360</v>
+        <v>7198017</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5396,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5406,7 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,10 +5423,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497189</v>
+        <v>121497208</v>
       </c>
       <c r="B44" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5449,34 +5439,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549139</v>
+        <v>548950</v>
       </c>
       <c r="R44" t="n">
-        <v>7198261</v>
+        <v>7198094</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497203</v>
+        <v>121497178</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5552,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548894</v>
+        <v>549168</v>
       </c>
       <c r="R45" t="n">
-        <v>7198284</v>
+        <v>7198189</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5615,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5625,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497206</v>
+        <v>121497209</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,34 +5668,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548952</v>
+        <v>549014</v>
       </c>
       <c r="R46" t="n">
-        <v>7198228</v>
+        <v>7198006</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497202</v>
+        <v>121497200</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>91160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,25 +3746,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548884</v>
+        <v>548885</v>
       </c>
       <c r="R29" t="n">
-        <v>7198316</v>
+        <v>7198318</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497200</v>
+        <v>121497190</v>
       </c>
       <c r="B30" t="n">
-        <v>91160</v>
+        <v>79691</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548885</v>
+        <v>549134</v>
       </c>
       <c r="R30" t="n">
-        <v>7198318</v>
+        <v>7198295</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497190</v>
+        <v>121497201</v>
       </c>
       <c r="B31" t="n">
-        <v>79691</v>
+        <v>91006</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549134</v>
+        <v>548884</v>
       </c>
       <c r="R31" t="n">
-        <v>7198295</v>
+        <v>7198317</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497201</v>
+        <v>121497171</v>
       </c>
       <c r="B32" t="n">
-        <v>91006</v>
+        <v>57356</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,34 +4086,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548884</v>
+        <v>549185</v>
       </c>
       <c r="R32" t="n">
-        <v>7198317</v>
+        <v>7198089</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4187,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497171</v>
+        <v>121497202</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,39 +4203,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549185</v>
+        <v>548884</v>
       </c>
       <c r="R33" t="n">
-        <v>7198089</v>
+        <v>7198316</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497165</v>
+        <v>121497180</v>
       </c>
       <c r="B34" t="n">
-        <v>79691</v>
+        <v>57509</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4315,34 +4315,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549099</v>
+        <v>549163</v>
       </c>
       <c r="R34" t="n">
-        <v>7197953</v>
+        <v>7198196</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4374,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,7 +4415,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497168</v>
+        <v>121497165</v>
       </c>
       <c r="B35" t="n">
         <v>79691</v>
@@ -4451,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549146</v>
+        <v>549099</v>
       </c>
       <c r="R35" t="n">
-        <v>7198067</v>
+        <v>7197953</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4486,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497180</v>
+        <v>121497168</v>
       </c>
       <c r="B36" t="n">
-        <v>57509</v>
+        <v>79691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,38 +4543,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549163</v>
+        <v>549146</v>
       </c>
       <c r="R36" t="n">
-        <v>7198196</v>
+        <v>7198067</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497176</v>
+        <v>121497208</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5215,34 +5215,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549196</v>
+        <v>548950</v>
       </c>
       <c r="R42" t="n">
-        <v>7198165</v>
+        <v>7198094</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5311,7 +5316,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497167</v>
+        <v>121497176</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549130</v>
+        <v>549196</v>
       </c>
       <c r="R43" t="n">
-        <v>7198017</v>
+        <v>7198165</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5386,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5396,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5423,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497208</v>
+        <v>121497167</v>
       </c>
       <c r="B44" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5439,39 +5444,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548950</v>
+        <v>549130</v>
       </c>
       <c r="R44" t="n">
-        <v>7198094</v>
+        <v>7198017</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497182</v>
+        <v>121497169</v>
       </c>
       <c r="B5" t="n">
-        <v>82393</v>
+        <v>79719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549164</v>
+        <v>549145</v>
       </c>
       <c r="R5" t="n">
-        <v>7198194</v>
+        <v>7198071</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497188</v>
+        <v>121497182</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549143</v>
+        <v>549164</v>
       </c>
       <c r="R6" t="n">
-        <v>7198251</v>
+        <v>7198194</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497169</v>
+        <v>121497188</v>
       </c>
       <c r="B7" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549145</v>
+        <v>549143</v>
       </c>
       <c r="R7" t="n">
-        <v>7198071</v>
+        <v>7198251</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497173</v>
+        <v>121497161</v>
       </c>
       <c r="B9" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,38 +1476,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549182</v>
+        <v>549102</v>
       </c>
       <c r="R9" t="n">
-        <v>7198123</v>
+        <v>7197710</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497161</v>
+        <v>121497173</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,43 +1822,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549102</v>
+        <v>549182</v>
       </c>
       <c r="R12" t="n">
-        <v>7197710</v>
+        <v>7198123</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497186</v>
+        <v>121497205</v>
       </c>
       <c r="B14" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,34 +2050,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549143</v>
+        <v>548901</v>
       </c>
       <c r="R14" t="n">
-        <v>7198250</v>
+        <v>7198259</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497204</v>
+        <v>121497193</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548901</v>
+        <v>549039</v>
       </c>
       <c r="R15" t="n">
-        <v>7198259</v>
+        <v>7198351</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497191</v>
+        <v>121497186</v>
       </c>
       <c r="B16" t="n">
-        <v>74699</v>
+        <v>79691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549086</v>
+        <v>549143</v>
       </c>
       <c r="R16" t="n">
-        <v>7198360</v>
+        <v>7198250</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497205</v>
+        <v>121497204</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,29 +2396,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
@@ -2487,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497193</v>
+        <v>121497191</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>74699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,43 +2504,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549039</v>
+        <v>549086</v>
       </c>
       <c r="R18" t="n">
-        <v>7198351</v>
+        <v>7198360</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497180</v>
+        <v>121497165</v>
       </c>
       <c r="B34" t="n">
-        <v>57509</v>
+        <v>79691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4315,38 +4315,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549163</v>
+        <v>549099</v>
       </c>
       <c r="R34" t="n">
-        <v>7198196</v>
+        <v>7197953</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,7 +4411,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497165</v>
+        <v>121497168</v>
       </c>
       <c r="B35" t="n">
         <v>79691</v>
@@ -4455,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549099</v>
+        <v>549146</v>
       </c>
       <c r="R35" t="n">
-        <v>7197953</v>
+        <v>7198067</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497168</v>
+        <v>121497180</v>
       </c>
       <c r="B36" t="n">
-        <v>79691</v>
+        <v>57509</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4543,34 +4539,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549146</v>
+        <v>549163</v>
       </c>
       <c r="R36" t="n">
-        <v>7198067</v>
+        <v>7198196</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497208</v>
+        <v>121497176</v>
       </c>
       <c r="B42" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5215,39 +5215,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548950</v>
+        <v>549196</v>
       </c>
       <c r="R42" t="n">
-        <v>7198094</v>
+        <v>7198165</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,7 +5311,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497176</v>
+        <v>121497167</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549196</v>
+        <v>549130</v>
       </c>
       <c r="R43" t="n">
-        <v>7198165</v>
+        <v>7198017</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,10 +5423,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497167</v>
+        <v>121497208</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5444,34 +5439,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549130</v>
+        <v>548950</v>
       </c>
       <c r="R44" t="n">
-        <v>7198017</v>
+        <v>7198094</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497175</v>
+        <v>121497161</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549197</v>
+        <v>549102</v>
       </c>
       <c r="R2" t="n">
-        <v>7198165</v>
+        <v>7197710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497174</v>
+        <v>121497185</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549183</v>
+        <v>549161</v>
       </c>
       <c r="R3" t="n">
-        <v>7198122</v>
+        <v>7198217</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497171</v>
+        <v>121497181</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549185</v>
+        <v>549164</v>
       </c>
       <c r="R4" t="n">
-        <v>7198089</v>
+        <v>7198195</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497177</v>
+        <v>121497167</v>
       </c>
       <c r="B5" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549194</v>
+        <v>549130</v>
       </c>
       <c r="R5" t="n">
-        <v>7198164</v>
+        <v>7198017</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497165</v>
+        <v>121497173</v>
       </c>
       <c r="B6" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549099</v>
+        <v>549182</v>
       </c>
       <c r="R6" t="n">
-        <v>7197953</v>
+        <v>7198123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497180</v>
+        <v>121497186</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>79698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,38 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549163</v>
+        <v>549143</v>
       </c>
       <c r="R7" t="n">
-        <v>7198196</v>
+        <v>7198250</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497202</v>
+        <v>121497178</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548884</v>
+        <v>549168</v>
       </c>
       <c r="R8" t="n">
-        <v>7198316</v>
+        <v>7198189</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497172</v>
+        <v>121497183</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549180</v>
+        <v>549164</v>
       </c>
       <c r="R9" t="n">
-        <v>7198099</v>
+        <v>7198193</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497190</v>
+        <v>121497209</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549134</v>
+        <v>549014</v>
       </c>
       <c r="R10" t="n">
-        <v>7198295</v>
+        <v>7198006</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497168</v>
+        <v>121497171</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549146</v>
+        <v>549185</v>
       </c>
       <c r="R11" t="n">
-        <v>7198067</v>
+        <v>7198089</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497163</v>
+        <v>121497202</v>
       </c>
       <c r="B12" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549066</v>
+        <v>548884</v>
       </c>
       <c r="R12" t="n">
-        <v>7197912</v>
+        <v>7198316</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497189</v>
+        <v>121497205</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549139</v>
+        <v>548901</v>
       </c>
       <c r="R13" t="n">
-        <v>7198261</v>
+        <v>7198259</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497207</v>
+        <v>121497165</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548954</v>
+        <v>549099</v>
       </c>
       <c r="R14" t="n">
-        <v>7198216</v>
+        <v>7197953</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497170</v>
+        <v>121497163</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,25 +2168,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549175</v>
+        <v>549066</v>
       </c>
       <c r="R15" t="n">
-        <v>7198087</v>
+        <v>7197912</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497187</v>
+        <v>121497175</v>
       </c>
       <c r="B16" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549143</v>
+        <v>549197</v>
       </c>
       <c r="R16" t="n">
-        <v>7198250</v>
+        <v>7198165</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497200</v>
+        <v>121497188</v>
       </c>
       <c r="B17" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,25 +2392,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548885</v>
+        <v>549143</v>
       </c>
       <c r="R17" t="n">
-        <v>7198318</v>
+        <v>7198251</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497191</v>
+        <v>121497170</v>
       </c>
       <c r="B18" t="n">
-        <v>74706</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,25 +2504,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549086</v>
+        <v>549175</v>
       </c>
       <c r="R18" t="n">
-        <v>7198360</v>
+        <v>7198087</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497178</v>
+        <v>121497195</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2616,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2638,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549168</v>
+        <v>548975</v>
       </c>
       <c r="R19" t="n">
-        <v>7198189</v>
+        <v>7198330</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497161</v>
+        <v>121497177</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,39 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549102</v>
+        <v>549194</v>
       </c>
       <c r="R20" t="n">
-        <v>7197710</v>
+        <v>7198164</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497194</v>
+        <v>121497190</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,21 +2844,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549039</v>
+        <v>549134</v>
       </c>
       <c r="R21" t="n">
-        <v>7198351</v>
+        <v>7198295</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497203</v>
+        <v>121497189</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2979,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548894</v>
+        <v>549139</v>
       </c>
       <c r="R22" t="n">
-        <v>7198284</v>
+        <v>7198261</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497164</v>
+        <v>121497176</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,25 +3064,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3091,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549099</v>
+        <v>549196</v>
       </c>
       <c r="R23" t="n">
-        <v>7197953</v>
+        <v>7198165</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,7 +3164,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497209</v>
+        <v>121497193</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3199,7 +3200,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3208,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549014</v>
+        <v>549039</v>
       </c>
       <c r="R24" t="n">
-        <v>7198006</v>
+        <v>7198351</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3243,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3253,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497193</v>
+        <v>121497169</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,43 +3293,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549039</v>
+        <v>549145</v>
       </c>
       <c r="R25" t="n">
-        <v>7198351</v>
+        <v>7198071</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3360,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3370,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497208</v>
+        <v>121497203</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,39 +3409,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548950</v>
+        <v>548894</v>
       </c>
       <c r="R26" t="n">
-        <v>7198094</v>
+        <v>7198284</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3477,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,7 +3505,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497188</v>
+        <v>121497204</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3554,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549143</v>
+        <v>548901</v>
       </c>
       <c r="R27" t="n">
-        <v>7198251</v>
+        <v>7198259</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3589,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497183</v>
+        <v>121497184</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,21 +3633,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549164</v>
+        <v>549161</v>
       </c>
       <c r="R28" t="n">
-        <v>7198193</v>
+        <v>7198220</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3701,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,10 +3729,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497166</v>
+        <v>121497168</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,21 +3745,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3778,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549115</v>
+        <v>549146</v>
       </c>
       <c r="R29" t="n">
-        <v>7197960</v>
+        <v>7198067</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3813,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497195</v>
+        <v>121497208</v>
       </c>
       <c r="B30" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,34 +3857,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548975</v>
+        <v>548950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198330</v>
+        <v>7198094</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3925,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497181</v>
+        <v>121497182</v>
       </c>
       <c r="B31" t="n">
-        <v>57373</v>
+        <v>82400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,29 +3974,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
@@ -4010,7 +4001,7 @@
         <v>549164</v>
       </c>
       <c r="R31" t="n">
-        <v>7198195</v>
+        <v>7198194</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4079,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497201</v>
+        <v>121497164</v>
       </c>
       <c r="B32" t="n">
-        <v>91014</v>
+        <v>79726</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4091,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548884</v>
+        <v>549099</v>
       </c>
       <c r="R32" t="n">
-        <v>7198317</v>
+        <v>7197953</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4154,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4164,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4191,7 +4182,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497204</v>
+        <v>121497166</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4231,10 +4222,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548901</v>
+        <v>549115</v>
       </c>
       <c r="R33" t="n">
-        <v>7198259</v>
+        <v>7197960</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4266,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4276,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497169</v>
+        <v>121497207</v>
       </c>
       <c r="B34" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4315,38 +4306,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549145</v>
+        <v>548954</v>
       </c>
       <c r="R34" t="n">
-        <v>7198071</v>
+        <v>7198216</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497205</v>
+        <v>121497200</v>
       </c>
       <c r="B35" t="n">
-        <v>57357</v>
+        <v>91168</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4427,43 +4423,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548901</v>
+        <v>548885</v>
       </c>
       <c r="R35" t="n">
-        <v>7198259</v>
+        <v>7198318</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4495,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4644,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497186</v>
+        <v>121497191</v>
       </c>
       <c r="B37" t="n">
-        <v>79698</v>
+        <v>74706</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4656,25 +4647,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4684,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549143</v>
+        <v>549086</v>
       </c>
       <c r="R37" t="n">
-        <v>7198250</v>
+        <v>7198360</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4719,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497179</v>
+        <v>121497187</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,21 +4763,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4796,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549168</v>
+        <v>549143</v>
       </c>
       <c r="R38" t="n">
-        <v>7198189</v>
+        <v>7198250</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4831,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4841,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,7 +4859,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497167</v>
+        <v>121497194</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -4908,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549130</v>
+        <v>549039</v>
       </c>
       <c r="R39" t="n">
-        <v>7198017</v>
+        <v>7198351</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4943,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,10 +4971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497182</v>
+        <v>121497201</v>
       </c>
       <c r="B40" t="n">
-        <v>82400</v>
+        <v>91014</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4996,21 +4987,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5020,10 +5011,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549164</v>
+        <v>548884</v>
       </c>
       <c r="R40" t="n">
-        <v>7198194</v>
+        <v>7198317</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5055,7 +5046,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +5056,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497184</v>
+        <v>121497172</v>
       </c>
       <c r="B41" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,34 +5099,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549161</v>
+        <v>549180</v>
       </c>
       <c r="R41" t="n">
-        <v>7198220</v>
+        <v>7198099</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5167,7 +5163,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,7 +5173,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5321,7 +5317,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497176</v>
+        <v>121497174</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5361,10 +5357,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549196</v>
+        <v>549183</v>
       </c>
       <c r="R43" t="n">
-        <v>7198165</v>
+        <v>7198122</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5396,7 +5392,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5406,7 +5402,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,7 +5429,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497185</v>
+        <v>121497179</v>
       </c>
       <c r="B44" t="n">
         <v>78616</v>
@@ -5473,10 +5469,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549161</v>
+        <v>549168</v>
       </c>
       <c r="R44" t="n">
-        <v>7198217</v>
+        <v>7198189</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5541,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497173</v>
+        <v>121497206</v>
       </c>
       <c r="B45" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5553,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5581,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549182</v>
+        <v>548952</v>
       </c>
       <c r="R45" t="n">
-        <v>7198123</v>
+        <v>7198228</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5653,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497206</v>
+        <v>121497180</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,34 +5669,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548952</v>
+        <v>549163</v>
       </c>
       <c r="R46" t="n">
-        <v>7198228</v>
+        <v>7198196</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497161</v>
+        <v>121497185</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549102</v>
+        <v>549161</v>
       </c>
       <c r="R2" t="n">
-        <v>7197710</v>
+        <v>7198217</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497185</v>
+        <v>121497181</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549161</v>
+        <v>549164</v>
       </c>
       <c r="R3" t="n">
-        <v>7198217</v>
+        <v>7198195</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497181</v>
+        <v>121497161</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549164</v>
+        <v>549102</v>
       </c>
       <c r="R4" t="n">
-        <v>7198195</v>
+        <v>7197710</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497178</v>
+        <v>121497183</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549168</v>
+        <v>549164</v>
       </c>
       <c r="R8" t="n">
-        <v>7198189</v>
+        <v>7198193</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497183</v>
+        <v>121497178</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549164</v>
+        <v>549168</v>
       </c>
       <c r="R9" t="n">
-        <v>7198193</v>
+        <v>7198189</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497171</v>
+        <v>121497202</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549185</v>
+        <v>548884</v>
       </c>
       <c r="R11" t="n">
-        <v>7198089</v>
+        <v>7198316</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497202</v>
+        <v>121497171</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548884</v>
+        <v>549185</v>
       </c>
       <c r="R12" t="n">
-        <v>7198316</v>
+        <v>7198089</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497188</v>
+        <v>121497170</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549143</v>
+        <v>549175</v>
       </c>
       <c r="R17" t="n">
-        <v>7198251</v>
+        <v>7198087</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497170</v>
+        <v>121497195</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549175</v>
+        <v>548975</v>
       </c>
       <c r="R18" t="n">
-        <v>7198087</v>
+        <v>7198330</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497195</v>
+        <v>121497188</v>
       </c>
       <c r="B19" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548975</v>
+        <v>549143</v>
       </c>
       <c r="R19" t="n">
-        <v>7198330</v>
+        <v>7198251</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497182</v>
+        <v>121497164</v>
       </c>
       <c r="B31" t="n">
-        <v>82400</v>
+        <v>79726</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549164</v>
+        <v>549099</v>
       </c>
       <c r="R31" t="n">
-        <v>7198194</v>
+        <v>7197953</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497164</v>
+        <v>121497182</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>82400</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549099</v>
+        <v>549164</v>
       </c>
       <c r="R32" t="n">
-        <v>7197953</v>
+        <v>7198194</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4635,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497191</v>
+        <v>121497187</v>
       </c>
       <c r="B37" t="n">
-        <v>74706</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4647,25 +4647,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549086</v>
+        <v>549143</v>
       </c>
       <c r="R37" t="n">
-        <v>7198360</v>
+        <v>7198250</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497187</v>
+        <v>121497191</v>
       </c>
       <c r="B38" t="n">
-        <v>79697</v>
+        <v>74706</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4759,25 +4759,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549143</v>
+        <v>549086</v>
       </c>
       <c r="R38" t="n">
-        <v>7198250</v>
+        <v>7198360</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497185</v>
+        <v>121497163</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549161</v>
+        <v>549066</v>
       </c>
       <c r="R2" t="n">
-        <v>7198217</v>
+        <v>7197912</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497181</v>
+        <v>121497161</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549164</v>
+        <v>549102</v>
       </c>
       <c r="R3" t="n">
-        <v>7198195</v>
+        <v>7197710</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497161</v>
+        <v>121497195</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549102</v>
+        <v>548975</v>
       </c>
       <c r="R4" t="n">
-        <v>7197710</v>
+        <v>7198330</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497167</v>
+        <v>121497177</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549130</v>
+        <v>549194</v>
       </c>
       <c r="R5" t="n">
-        <v>7198017</v>
+        <v>7198164</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497173</v>
+        <v>121497171</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549182</v>
+        <v>549185</v>
       </c>
       <c r="R6" t="n">
-        <v>7198123</v>
+        <v>7198089</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497186</v>
+        <v>121497170</v>
       </c>
       <c r="B7" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549143</v>
+        <v>549175</v>
       </c>
       <c r="R7" t="n">
-        <v>7198250</v>
+        <v>7198087</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497183</v>
+        <v>121497191</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549164</v>
+        <v>549086</v>
       </c>
       <c r="R8" t="n">
-        <v>7198193</v>
+        <v>7198360</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497178</v>
+        <v>121497174</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549168</v>
+        <v>549183</v>
       </c>
       <c r="R9" t="n">
-        <v>7198189</v>
+        <v>7198122</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497209</v>
+        <v>121497206</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549014</v>
+        <v>548952</v>
       </c>
       <c r="R10" t="n">
-        <v>7198006</v>
+        <v>7198228</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497202</v>
+        <v>121497184</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548884</v>
+        <v>549161</v>
       </c>
       <c r="R11" t="n">
-        <v>7198316</v>
+        <v>7198220</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497171</v>
+        <v>121497194</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549185</v>
+        <v>549039</v>
       </c>
       <c r="R12" t="n">
-        <v>7198089</v>
+        <v>7198351</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497205</v>
+        <v>121497178</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,43 +1929,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548901</v>
+        <v>549168</v>
       </c>
       <c r="R13" t="n">
-        <v>7198259</v>
+        <v>7198189</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497165</v>
+        <v>121497201</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>91014</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549099</v>
+        <v>548884</v>
       </c>
       <c r="R14" t="n">
-        <v>7197953</v>
+        <v>7198317</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497163</v>
+        <v>121497188</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549066</v>
+        <v>549143</v>
       </c>
       <c r="R15" t="n">
-        <v>7197912</v>
+        <v>7198251</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497175</v>
+        <v>121497168</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>79698</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549197</v>
+        <v>549146</v>
       </c>
       <c r="R16" t="n">
-        <v>7198165</v>
+        <v>7198067</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497170</v>
+        <v>121497173</v>
       </c>
       <c r="B17" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,25 +2377,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549175</v>
+        <v>549182</v>
       </c>
       <c r="R17" t="n">
-        <v>7198087</v>
+        <v>7198123</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497195</v>
+        <v>121497189</v>
       </c>
       <c r="B18" t="n">
         <v>79698</v>
@@ -2532,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548975</v>
+        <v>549139</v>
       </c>
       <c r="R18" t="n">
-        <v>7198330</v>
+        <v>7198261</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497188</v>
+        <v>121497162</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,34 +2605,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549143</v>
+        <v>549089</v>
       </c>
       <c r="R19" t="n">
-        <v>7198251</v>
+        <v>7197751</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497177</v>
+        <v>121497176</v>
       </c>
       <c r="B20" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549194</v>
+        <v>549196</v>
       </c>
       <c r="R20" t="n">
-        <v>7198164</v>
+        <v>7198165</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2828,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497190</v>
+        <v>121497175</v>
       </c>
       <c r="B21" t="n">
-        <v>79698</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549134</v>
+        <v>549197</v>
       </c>
       <c r="R21" t="n">
-        <v>7198295</v>
+        <v>7198165</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497189</v>
+        <v>121497200</v>
       </c>
       <c r="B22" t="n">
-        <v>79698</v>
+        <v>91168</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2952,25 +2942,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2970,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549139</v>
+        <v>548885</v>
       </c>
       <c r="R22" t="n">
-        <v>7198261</v>
+        <v>7198318</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497176</v>
+        <v>121497207</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,34 +3058,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549196</v>
+        <v>548954</v>
       </c>
       <c r="R23" t="n">
-        <v>7198165</v>
+        <v>7198216</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,7 +3159,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497193</v>
+        <v>121497172</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3200,7 +3195,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3209,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549039</v>
+        <v>549180</v>
       </c>
       <c r="R24" t="n">
-        <v>7198351</v>
+        <v>7198099</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3244,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497169</v>
+        <v>121497209</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3293,38 +3288,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549145</v>
+        <v>549014</v>
       </c>
       <c r="R25" t="n">
-        <v>7198071</v>
+        <v>7198006</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497203</v>
+        <v>121497166</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548894</v>
+        <v>549115</v>
       </c>
       <c r="R26" t="n">
-        <v>7198284</v>
+        <v>7197960</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,7 +3505,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497204</v>
+        <v>121497183</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548901</v>
+        <v>549164</v>
       </c>
       <c r="R27" t="n">
-        <v>7198259</v>
+        <v>7198193</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,7 +3617,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497184</v>
+        <v>121497190</v>
       </c>
       <c r="B28" t="n">
         <v>79698</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549161</v>
+        <v>549134</v>
       </c>
       <c r="R28" t="n">
-        <v>7198220</v>
+        <v>7198295</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,10 +3729,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497168</v>
+        <v>121497181</v>
       </c>
       <c r="B29" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3745,34 +3745,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549146</v>
+        <v>549164</v>
       </c>
       <c r="R29" t="n">
-        <v>7198067</v>
+        <v>7198195</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497208</v>
+        <v>121497182</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,39 +3862,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548950</v>
+        <v>549164</v>
       </c>
       <c r="R30" t="n">
-        <v>7198094</v>
+        <v>7198194</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497164</v>
+        <v>121497180</v>
       </c>
       <c r="B31" t="n">
-        <v>79726</v>
+        <v>57510</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,38 +3970,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549099</v>
+        <v>549163</v>
       </c>
       <c r="R31" t="n">
-        <v>7197953</v>
+        <v>7198196</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4037,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4074,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497182</v>
+        <v>121497187</v>
       </c>
       <c r="B32" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,21 +4090,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4110,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549164</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>7198194</v>
+        <v>7198250</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4149,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4159,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497166</v>
+        <v>121497193</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,34 +4202,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549115</v>
+        <v>549039</v>
       </c>
       <c r="R33" t="n">
-        <v>7197960</v>
+        <v>7198351</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4266,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4276,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4303,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497207</v>
+        <v>121497204</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,39 +4319,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548954</v>
+        <v>548901</v>
       </c>
       <c r="R34" t="n">
-        <v>7198216</v>
+        <v>7198259</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4374,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,10 +4415,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497200</v>
+        <v>121497179</v>
       </c>
       <c r="B35" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,25 +4427,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4451,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548885</v>
+        <v>549168</v>
       </c>
       <c r="R35" t="n">
-        <v>7198318</v>
+        <v>7198189</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4486,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497192</v>
+        <v>121497164</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,25 +4539,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4563,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549086</v>
+        <v>549099</v>
       </c>
       <c r="R36" t="n">
-        <v>7198360</v>
+        <v>7197953</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497187</v>
+        <v>121497208</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,34 +4655,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549143</v>
+        <v>548950</v>
       </c>
       <c r="R37" t="n">
-        <v>7198250</v>
+        <v>7198094</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4756,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497191</v>
+        <v>121497165</v>
       </c>
       <c r="B38" t="n">
-        <v>74706</v>
+        <v>79698</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4759,25 +4768,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4787,10 +4796,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549086</v>
+        <v>549099</v>
       </c>
       <c r="R38" t="n">
-        <v>7198360</v>
+        <v>7197953</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4831,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4841,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,7 +4868,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497194</v>
+        <v>121497192</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -4899,10 +4908,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549039</v>
+        <v>549086</v>
       </c>
       <c r="R39" t="n">
-        <v>7198351</v>
+        <v>7198360</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4943,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4953,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4971,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497201</v>
+        <v>121497203</v>
       </c>
       <c r="B40" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4987,21 +4996,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5011,10 +5020,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548884</v>
+        <v>548894</v>
       </c>
       <c r="R40" t="n">
-        <v>7198317</v>
+        <v>7198284</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5046,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5056,7 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,10 +5092,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497172</v>
+        <v>121497167</v>
       </c>
       <c r="B41" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5099,39 +5108,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549180</v>
+        <v>549130</v>
       </c>
       <c r="R41" t="n">
-        <v>7198099</v>
+        <v>7198017</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5173,7 +5177,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497162</v>
+        <v>121497185</v>
       </c>
       <c r="B42" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5216,39 +5220,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549089</v>
+        <v>549161</v>
       </c>
       <c r="R42" t="n">
-        <v>7197751</v>
+        <v>7198217</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5280,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5290,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5317,10 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497174</v>
+        <v>121497169</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5329,25 +5328,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5357,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549183</v>
+        <v>549145</v>
       </c>
       <c r="R43" t="n">
-        <v>7198122</v>
+        <v>7198071</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5392,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5402,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,7 +5428,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497179</v>
+        <v>121497202</v>
       </c>
       <c r="B44" t="n">
         <v>78616</v>
@@ -5469,10 +5468,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549168</v>
+        <v>548884</v>
       </c>
       <c r="R44" t="n">
-        <v>7198189</v>
+        <v>7198316</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5504,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5514,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5541,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497206</v>
+        <v>121497186</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,21 +5556,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5581,10 +5580,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548952</v>
+        <v>549143</v>
       </c>
       <c r="R45" t="n">
-        <v>7198228</v>
+        <v>7198250</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5616,7 +5615,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5625,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,10 +5652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497180</v>
+        <v>121497205</v>
       </c>
       <c r="B46" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5669,26 +5668,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549163</v>
+        <v>548901</v>
       </c>
       <c r="R46" t="n">
-        <v>7198196</v>
+        <v>7198259</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497163</v>
+        <v>121497161</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549066</v>
+        <v>549102</v>
       </c>
       <c r="R2" t="n">
-        <v>7197912</v>
+        <v>7197710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497161</v>
+        <v>121497163</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549102</v>
+        <v>549066</v>
       </c>
       <c r="R3" t="n">
-        <v>7197710</v>
+        <v>7197912</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497178</v>
+        <v>121497188</v>
       </c>
       <c r="B13" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549168</v>
+        <v>549143</v>
       </c>
       <c r="R13" t="n">
-        <v>7198189</v>
+        <v>7198251</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497201</v>
+        <v>121497178</v>
       </c>
       <c r="B14" t="n">
-        <v>91014</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,25 +2041,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548884</v>
+        <v>549168</v>
       </c>
       <c r="R14" t="n">
-        <v>7198317</v>
+        <v>7198189</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497188</v>
+        <v>121497201</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549143</v>
+        <v>548884</v>
       </c>
       <c r="R15" t="n">
-        <v>7198251</v>
+        <v>7198317</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497187</v>
+        <v>121497204</v>
       </c>
       <c r="B32" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>548901</v>
       </c>
       <c r="R32" t="n">
-        <v>7198250</v>
+        <v>7198259</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497193</v>
+        <v>121497179</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4202,39 +4202,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549039</v>
+        <v>549168</v>
       </c>
       <c r="R33" t="n">
-        <v>7198351</v>
+        <v>7198189</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4266,7 +4261,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4276,7 +4271,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,10 +4298,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497204</v>
+        <v>121497187</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4319,21 +4314,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4343,10 +4338,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548901</v>
+        <v>549143</v>
       </c>
       <c r="R34" t="n">
-        <v>7198259</v>
+        <v>7198250</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4378,7 +4373,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4383,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4410,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497179</v>
+        <v>121497193</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4431,34 +4426,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549168</v>
+        <v>549039</v>
       </c>
       <c r="R35" t="n">
-        <v>7198189</v>
+        <v>7198351</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497169</v>
+        <v>121497186</v>
       </c>
       <c r="B43" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5328,25 +5328,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549145</v>
+        <v>549143</v>
       </c>
       <c r="R43" t="n">
-        <v>7198071</v>
+        <v>7198250</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497202</v>
+        <v>121497169</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548884</v>
+        <v>549145</v>
       </c>
       <c r="R44" t="n">
-        <v>7198316</v>
+        <v>7198071</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497186</v>
+        <v>121497202</v>
       </c>
       <c r="B45" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549143</v>
+        <v>548884</v>
       </c>
       <c r="R45" t="n">
-        <v>7198250</v>
+        <v>7198316</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497161</v>
+        <v>121497174</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549102</v>
+        <v>549183</v>
       </c>
       <c r="R2" t="n">
-        <v>7197710</v>
+        <v>7198122</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497163</v>
+        <v>121497181</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549066</v>
+        <v>549164</v>
       </c>
       <c r="R3" t="n">
-        <v>7197912</v>
+        <v>7198195</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497195</v>
+        <v>121497182</v>
       </c>
       <c r="B4" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548975</v>
+        <v>549164</v>
       </c>
       <c r="R4" t="n">
-        <v>7198330</v>
+        <v>7198194</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497177</v>
+        <v>121497200</v>
       </c>
       <c r="B5" t="n">
-        <v>79698</v>
+        <v>91168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549194</v>
+        <v>548885</v>
       </c>
       <c r="R5" t="n">
-        <v>7198164</v>
+        <v>7198318</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497171</v>
+        <v>121497205</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549185</v>
+        <v>548901</v>
       </c>
       <c r="R6" t="n">
-        <v>7198089</v>
+        <v>7198259</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497170</v>
+        <v>121497171</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549175</v>
+        <v>549185</v>
       </c>
       <c r="R7" t="n">
-        <v>7198087</v>
+        <v>7198089</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497191</v>
+        <v>121497169</v>
       </c>
       <c r="B8" t="n">
-        <v>74706</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549086</v>
+        <v>549145</v>
       </c>
       <c r="R8" t="n">
-        <v>7198360</v>
+        <v>7198071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497174</v>
+        <v>121497162</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549183</v>
+        <v>549089</v>
       </c>
       <c r="R9" t="n">
-        <v>7198122</v>
+        <v>7197751</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497206</v>
+        <v>121497165</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548952</v>
+        <v>549099</v>
       </c>
       <c r="R10" t="n">
-        <v>7198228</v>
+        <v>7197953</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497184</v>
+        <v>121497190</v>
       </c>
       <c r="B11" t="n">
         <v>79698</v>
@@ -1733,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549161</v>
+        <v>549134</v>
       </c>
       <c r="R11" t="n">
-        <v>7198220</v>
+        <v>7198295</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497194</v>
+        <v>121497189</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549039</v>
+        <v>549139</v>
       </c>
       <c r="R12" t="n">
-        <v>7198351</v>
+        <v>7198261</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497188</v>
+        <v>121497201</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549143</v>
+        <v>548884</v>
       </c>
       <c r="R13" t="n">
-        <v>7198251</v>
+        <v>7198317</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497178</v>
+        <v>121497193</v>
       </c>
       <c r="B14" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,38 +2051,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549168</v>
+        <v>549039</v>
       </c>
       <c r="R14" t="n">
-        <v>7198189</v>
+        <v>7198351</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497201</v>
+        <v>121497194</v>
       </c>
       <c r="B15" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548884</v>
+        <v>549039</v>
       </c>
       <c r="R15" t="n">
-        <v>7198317</v>
+        <v>7198351</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497168</v>
+        <v>121497204</v>
       </c>
       <c r="B16" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549146</v>
+        <v>548901</v>
       </c>
       <c r="R16" t="n">
-        <v>7198067</v>
+        <v>7198259</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497173</v>
+        <v>121497180</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>57510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,38 +2392,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549182</v>
+        <v>549163</v>
       </c>
       <c r="R17" t="n">
-        <v>7198123</v>
+        <v>7198196</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2469,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497189</v>
+        <v>121497170</v>
       </c>
       <c r="B18" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,21 +2512,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549139</v>
+        <v>549175</v>
       </c>
       <c r="R18" t="n">
-        <v>7198261</v>
+        <v>7198087</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,7 +2608,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497162</v>
+        <v>121497172</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2634,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549089</v>
+        <v>549180</v>
       </c>
       <c r="R19" t="n">
-        <v>7197751</v>
+        <v>7198099</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497176</v>
+        <v>121497208</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,34 +2741,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549196</v>
+        <v>548950</v>
       </c>
       <c r="R20" t="n">
-        <v>7198165</v>
+        <v>7198094</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497175</v>
+        <v>121497161</v>
       </c>
       <c r="B21" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,34 +2858,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549197</v>
+        <v>549102</v>
       </c>
       <c r="R21" t="n">
-        <v>7198165</v>
+        <v>7197710</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497200</v>
+        <v>121497192</v>
       </c>
       <c r="B22" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,25 +2971,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +2999,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548885</v>
+        <v>549086</v>
       </c>
       <c r="R22" t="n">
-        <v>7198318</v>
+        <v>7198360</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497207</v>
+        <v>121497175</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,39 +3087,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548954</v>
+        <v>549197</v>
       </c>
       <c r="R23" t="n">
-        <v>7198216</v>
+        <v>7198165</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3183,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497172</v>
+        <v>121497187</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,39 +3199,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549180</v>
+        <v>549143</v>
       </c>
       <c r="R24" t="n">
-        <v>7198099</v>
+        <v>7198250</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497209</v>
+        <v>121497173</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3288,43 +3307,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549014</v>
+        <v>549182</v>
       </c>
       <c r="R25" t="n">
-        <v>7198006</v>
+        <v>7198123</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,7 +3407,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497166</v>
+        <v>121497185</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3433,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549115</v>
+        <v>549161</v>
       </c>
       <c r="R26" t="n">
-        <v>7197960</v>
+        <v>7198217</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3468,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,7 +3519,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497183</v>
+        <v>121497202</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3545,10 +3559,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549164</v>
+        <v>548884</v>
       </c>
       <c r="R27" t="n">
-        <v>7198193</v>
+        <v>7198316</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,7 +3631,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497190</v>
+        <v>121497168</v>
       </c>
       <c r="B28" t="n">
         <v>79698</v>
@@ -3657,10 +3671,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549134</v>
+        <v>549146</v>
       </c>
       <c r="R28" t="n">
-        <v>7198295</v>
+        <v>7198067</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3706,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3716,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,10 +3743,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497181</v>
+        <v>121497184</v>
       </c>
       <c r="B29" t="n">
-        <v>57373</v>
+        <v>79698</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3745,39 +3759,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549164</v>
+        <v>549161</v>
       </c>
       <c r="R29" t="n">
-        <v>7198195</v>
+        <v>7198220</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3818,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3828,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497182</v>
+        <v>121497191</v>
       </c>
       <c r="B30" t="n">
-        <v>82400</v>
+        <v>74706</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,25 +3867,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3895,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549164</v>
+        <v>549086</v>
       </c>
       <c r="R30" t="n">
-        <v>7198194</v>
+        <v>7198360</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3930,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3940,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497180</v>
+        <v>121497166</v>
       </c>
       <c r="B31" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,38 +3983,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549163</v>
+        <v>549115</v>
       </c>
       <c r="R31" t="n">
-        <v>7198196</v>
+        <v>7197960</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4047,7 +4052,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,7 +4079,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497204</v>
+        <v>121497179</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548901</v>
+        <v>549168</v>
       </c>
       <c r="R32" t="n">
-        <v>7198259</v>
+        <v>7198189</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4149,7 +4154,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4164,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,7 +4191,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497179</v>
+        <v>121497183</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549168</v>
+        <v>549164</v>
       </c>
       <c r="R33" t="n">
-        <v>7198189</v>
+        <v>7198193</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4261,7 +4266,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4271,7 +4276,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,10 +4303,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497187</v>
+        <v>121497209</v>
       </c>
       <c r="B34" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4314,34 +4319,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549143</v>
+        <v>549014</v>
       </c>
       <c r="R34" t="n">
-        <v>7198250</v>
+        <v>7198006</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4373,7 +4383,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4383,7 +4393,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4410,10 +4420,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497193</v>
+        <v>121497178</v>
       </c>
       <c r="B35" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4422,43 +4432,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549039</v>
+        <v>549168</v>
       </c>
       <c r="R35" t="n">
-        <v>7198351</v>
+        <v>7198189</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4490,7 +4495,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4505,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4532,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497164</v>
+        <v>121497176</v>
       </c>
       <c r="B36" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,25 +4544,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4567,10 +4572,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549099</v>
+        <v>549196</v>
       </c>
       <c r="R36" t="n">
-        <v>7197953</v>
+        <v>7198165</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4602,7 +4607,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4617,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,10 +4644,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497208</v>
+        <v>121497177</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,39 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548950</v>
+        <v>549194</v>
       </c>
       <c r="R37" t="n">
-        <v>7198094</v>
+        <v>7198164</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,7 +4756,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497165</v>
+        <v>121497186</v>
       </c>
       <c r="B38" t="n">
         <v>79698</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549099</v>
+        <v>549143</v>
       </c>
       <c r="R38" t="n">
-        <v>7197953</v>
+        <v>7198250</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,10 +4868,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497192</v>
+        <v>121497164</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4880,25 +4880,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549086</v>
+        <v>549099</v>
       </c>
       <c r="R39" t="n">
-        <v>7198360</v>
+        <v>7197953</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497203</v>
+        <v>121497163</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,25 +4992,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548894</v>
+        <v>549066</v>
       </c>
       <c r="R40" t="n">
-        <v>7198284</v>
+        <v>7197912</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,7 +5204,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497185</v>
+        <v>121497206</v>
       </c>
       <c r="B42" t="n">
         <v>78616</v>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549161</v>
+        <v>548952</v>
       </c>
       <c r="R42" t="n">
-        <v>7198217</v>
+        <v>7198228</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497186</v>
+        <v>121497207</v>
       </c>
       <c r="B43" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,34 +5332,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549143</v>
+        <v>548954</v>
       </c>
       <c r="R43" t="n">
-        <v>7198250</v>
+        <v>7198216</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5391,7 +5396,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5401,7 +5406,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,10 +5433,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497169</v>
+        <v>121497195</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,25 +5445,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5468,10 +5473,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549145</v>
+        <v>548975</v>
       </c>
       <c r="R44" t="n">
-        <v>7198071</v>
+        <v>7198330</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5503,7 +5508,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5513,7 +5518,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,7 +5545,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497202</v>
+        <v>121497188</v>
       </c>
       <c r="B45" t="n">
         <v>78616</v>
@@ -5580,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548884</v>
+        <v>549143</v>
       </c>
       <c r="R45" t="n">
-        <v>7198316</v>
+        <v>7198251</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5615,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5625,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497205</v>
+        <v>121497203</v>
       </c>
       <c r="B46" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5668,39 +5673,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548901</v>
+        <v>548894</v>
       </c>
       <c r="R46" t="n">
-        <v>7198259</v>
+        <v>7198284</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19934-2023 artfynd.xlsx
+++ b/artfynd/A 19934-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497174</v>
+        <v>121497201</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549183</v>
+        <v>548884</v>
       </c>
       <c r="R2" t="n">
-        <v>7198122</v>
+        <v>7198317</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497181</v>
+        <v>121497200</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549164</v>
+        <v>548885</v>
       </c>
       <c r="R3" t="n">
-        <v>7198195</v>
+        <v>7198318</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,12 +892,7 @@
         <v>121497182</v>
       </c>
       <c r="B4" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497200</v>
+        <v>121497165</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548885</v>
+        <v>549099</v>
       </c>
       <c r="R5" t="n">
-        <v>7198318</v>
+        <v>7197953</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497205</v>
+        <v>121497168</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548901</v>
+        <v>549146</v>
       </c>
       <c r="R6" t="n">
-        <v>7198259</v>
+        <v>7198067</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497171</v>
+        <v>121497177</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549185</v>
+        <v>549194</v>
       </c>
       <c r="R7" t="n">
-        <v>7198089</v>
+        <v>7198164</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121497169</v>
+        <v>121497184</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549145</v>
+        <v>549161</v>
       </c>
       <c r="R8" t="n">
-        <v>7198071</v>
+        <v>7198220</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121497162</v>
+        <v>121497186</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,39 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549089</v>
+        <v>549143</v>
       </c>
       <c r="R9" t="n">
-        <v>7197751</v>
+        <v>7198250</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121497165</v>
+        <v>121497189</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549099</v>
+        <v>549139</v>
       </c>
       <c r="R10" t="n">
-        <v>7197953</v>
+        <v>7198261</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,12 +1641,7 @@
         <v>121497190</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497189</v>
+        <v>121497195</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549139</v>
+        <v>548975</v>
       </c>
       <c r="R12" t="n">
-        <v>7198261</v>
+        <v>7198330</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497201</v>
+        <v>121497197</v>
       </c>
       <c r="B13" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548884</v>
+        <v>548913</v>
       </c>
       <c r="R13" t="n">
-        <v>7198317</v>
+        <v>7198352</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,55 +1959,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497193</v>
+        <v>121497166</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549039</v>
+        <v>549115</v>
       </c>
       <c r="R14" t="n">
-        <v>7198351</v>
+        <v>7197960</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,19 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497194</v>
+        <v>121497167</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2196,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549039</v>
+        <v>549130</v>
       </c>
       <c r="R15" t="n">
-        <v>7198351</v>
+        <v>7198017</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,19 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497204</v>
+        <v>121497174</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2308,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548901</v>
+        <v>549183</v>
       </c>
       <c r="R16" t="n">
-        <v>7198259</v>
+        <v>7198122</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,54 +2280,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497180</v>
+        <v>121497176</v>
       </c>
       <c r="B17" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549163</v>
+        <v>549196</v>
       </c>
       <c r="R17" t="n">
-        <v>7198196</v>
+        <v>7198165</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,37 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497170</v>
+        <v>121497179</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549175</v>
+        <v>549168</v>
       </c>
       <c r="R18" t="n">
-        <v>7198087</v>
+        <v>7198189</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,55 +2494,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497172</v>
+        <v>121497183</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549180</v>
+        <v>549164</v>
       </c>
       <c r="R19" t="n">
-        <v>7198099</v>
+        <v>7198193</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,55 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497208</v>
+        <v>121497185</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548950</v>
+        <v>549161</v>
       </c>
       <c r="R20" t="n">
-        <v>7198094</v>
+        <v>7198217</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2805,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,55 +2708,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497161</v>
+        <v>121497188</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549102</v>
+        <v>549143</v>
       </c>
       <c r="R21" t="n">
-        <v>7197710</v>
+        <v>7198251</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,16 +2818,11 @@
         <v>121497192</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3071,37 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497175</v>
+        <v>121497194</v>
       </c>
       <c r="B23" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3111,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549197</v>
+        <v>549039</v>
       </c>
       <c r="R23" t="n">
-        <v>7198165</v>
+        <v>7198351</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,37 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497187</v>
+        <v>121497198</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3223,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549143</v>
+        <v>548913</v>
       </c>
       <c r="R24" t="n">
-        <v>7198250</v>
+        <v>7198352</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3258,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,37 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121497173</v>
+        <v>121497202</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3335,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549182</v>
+        <v>548884</v>
       </c>
       <c r="R25" t="n">
-        <v>7198123</v>
+        <v>7198316</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3370,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,19 +3243,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121497185</v>
+        <v>121497203</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3447,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549161</v>
+        <v>548894</v>
       </c>
       <c r="R26" t="n">
-        <v>7198217</v>
+        <v>7198284</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3482,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,19 +3350,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121497202</v>
+        <v>121497204</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3559,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548884</v>
+        <v>548901</v>
       </c>
       <c r="R27" t="n">
-        <v>7198316</v>
+        <v>7198259</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3594,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,37 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121497168</v>
+        <v>121497206</v>
       </c>
       <c r="B28" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3671,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549146</v>
+        <v>548952</v>
       </c>
       <c r="R28" t="n">
-        <v>7198067</v>
+        <v>7198228</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3706,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3716,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,37 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121497184</v>
+        <v>121497191</v>
       </c>
       <c r="B29" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3783,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549161</v>
+        <v>549086</v>
       </c>
       <c r="R29" t="n">
-        <v>7198220</v>
+        <v>7198360</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3818,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3828,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,37 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121497191</v>
+        <v>121497170</v>
       </c>
       <c r="B30" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3895,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549086</v>
+        <v>549175</v>
       </c>
       <c r="R30" t="n">
-        <v>7198360</v>
+        <v>7198087</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3930,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3940,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,15 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121497166</v>
+        <v>121497187</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4007,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549115</v>
+        <v>549143</v>
       </c>
       <c r="R31" t="n">
-        <v>7197960</v>
+        <v>7198250</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4042,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4052,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,15 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121497179</v>
+        <v>121497196</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4095,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549168</v>
+        <v>548913</v>
       </c>
       <c r="R32" t="n">
-        <v>7198189</v>
+        <v>7198352</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4154,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4164,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4191,37 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121497183</v>
+        <v>121497164</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4231,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549164</v>
+        <v>549099</v>
       </c>
       <c r="R33" t="n">
-        <v>7198193</v>
+        <v>7197953</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4266,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4276,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,55 +4099,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121497209</v>
+        <v>121497169</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549014</v>
+        <v>549145</v>
       </c>
       <c r="R34" t="n">
-        <v>7198006</v>
+        <v>7198071</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4383,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4393,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,15 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121497178</v>
+        <v>121497173</v>
       </c>
       <c r="B35" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4460,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549168</v>
+        <v>549182</v>
       </c>
       <c r="R35" t="n">
-        <v>7198189</v>
+        <v>7198123</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4495,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4532,37 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121497176</v>
+        <v>121497178</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4572,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549196</v>
+        <v>549168</v>
       </c>
       <c r="R36" t="n">
-        <v>7198165</v>
+        <v>7198189</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4607,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4644,50 +4420,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121497177</v>
+        <v>121497181</v>
       </c>
       <c r="B37" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549194</v>
+        <v>549164</v>
       </c>
       <c r="R37" t="n">
-        <v>7198164</v>
+        <v>7198195</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4719,7 +4495,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4505,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,15 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121497186</v>
+        <v>121497161</v>
       </c>
       <c r="B38" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4772,34 +4543,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R38" t="n">
-        <v>7198250</v>
+        <v>7197710</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4831,7 +4607,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4841,7 +4617,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,50 +4644,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121497164</v>
+        <v>121497162</v>
       </c>
       <c r="B39" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549099</v>
+        <v>549089</v>
       </c>
       <c r="R39" t="n">
-        <v>7197953</v>
+        <v>7197751</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4943,7 +4719,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4729,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,50 +4756,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121497163</v>
+        <v>121497171</v>
       </c>
       <c r="B40" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549066</v>
+        <v>549185</v>
       </c>
       <c r="R40" t="n">
-        <v>7197912</v>
+        <v>7198089</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5055,7 +4831,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +4841,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,15 +4868,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121497167</v>
+        <v>121497172</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,34 +4879,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549130</v>
+        <v>549180</v>
       </c>
       <c r="R41" t="n">
-        <v>7198017</v>
+        <v>7198099</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5167,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,15 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121497206</v>
+        <v>121497193</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5220,34 +4991,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548952</v>
+        <v>549039</v>
       </c>
       <c r="R42" t="n">
-        <v>7198228</v>
+        <v>7198351</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5279,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,15 +5092,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121497207</v>
+        <v>121497199</v>
       </c>
       <c r="B43" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,7 +5123,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5361,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548954</v>
+        <v>548903</v>
       </c>
       <c r="R43" t="n">
-        <v>7198216</v>
+        <v>7198349</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5396,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5406,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,15 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121497195</v>
+        <v>121497205</v>
       </c>
       <c r="B44" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,34 +5215,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548975</v>
+        <v>548901</v>
       </c>
       <c r="R44" t="n">
-        <v>7198330</v>
+        <v>7198259</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5508,7 +5279,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5518,7 +5289,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,15 +5316,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121497188</v>
+        <v>121497207</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5561,34 +5327,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549143</v>
+        <v>548954</v>
       </c>
       <c r="R45" t="n">
-        <v>7198251</v>
+        <v>7198216</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5620,7 +5391,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5401,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,15 +5428,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121497203</v>
+        <v>121497208</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5673,34 +5439,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548894</v>
+        <v>548950</v>
       </c>
       <c r="R46" t="n">
-        <v>7198284</v>
+        <v>7198094</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5732,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5766,6 +5537,448 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121497209</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>549014</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7198006</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121497210</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>549013</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7198008</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121497180</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>549163</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7198196</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121497163</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>549066</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7197912</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
